--- a/3DO.xlsx
+++ b/3DO.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="311">
   <si>
     <t>FLAGS</t>
   </si>
@@ -948,6 +948,9 @@
   </si>
   <si>
     <t>DSP DMA reads a maximum of 12 bytes (3 words) and generates a DMAREQ sequence.</t>
+  </si>
+  <si>
+    <t>end DMA block and length, no loop</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +1080,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1367,11 +1370,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1572,6 +1584,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2030,16 +2051,16 @@
       <c r="A1" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="76" t="s">
+      <c r="B1" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="16">
@@ -2068,24 +2089,24 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="82" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="80" t="s">
         <v>177</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77" t="s">
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80" t="s">
         <v>272</v>
       </c>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="78"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="81"/>
     </row>
     <row r="4" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="75"/>
+      <c r="A4" s="78"/>
       <c r="B4" s="19" t="s">
         <v>152</v>
       </c>
@@ -2115,36 +2136,36 @@
       <c r="A5" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="82" t="s">
         <v>163</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="80" t="s">
         <v>175</v>
       </c>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77" t="s">
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80" t="s">
         <v>176</v>
       </c>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="78"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="81"/>
     </row>
     <row r="7" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="75"/>
+      <c r="A7" s="78"/>
       <c r="B7" s="19" t="s">
         <v>152</v>
       </c>
@@ -2171,24 +2192,24 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="79" t="s">
+      <c r="A8" s="82" t="s">
         <v>160</v>
       </c>
-      <c r="B8" s="77" t="s">
+      <c r="B8" s="80" t="s">
         <v>174</v>
       </c>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77" t="s">
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80" t="s">
         <v>173</v>
       </c>
-      <c r="G8" s="77"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="78"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="81"/>
     </row>
     <row r="9" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="80"/>
+      <c r="A9" s="83"/>
       <c r="B9" s="21" t="s">
         <v>152</v>
       </c>
@@ -2215,24 +2236,24 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="79" t="s">
+      <c r="A10" s="82" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="80" t="s">
         <v>171</v>
       </c>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77" t="s">
+      <c r="C10" s="80"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="80" t="s">
         <v>172</v>
       </c>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="78"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="81"/>
     </row>
     <row r="11" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="80"/>
+      <c r="A11" s="83"/>
       <c r="B11" s="21" t="s">
         <v>152</v>
       </c>
@@ -2259,24 +2280,24 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="79" t="s">
+      <c r="A12" s="82" t="s">
         <v>158</v>
       </c>
-      <c r="B12" s="77" t="s">
+      <c r="B12" s="80" t="s">
         <v>170</v>
       </c>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77" t="s">
+      <c r="C12" s="80"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="80" t="s">
         <v>169</v>
       </c>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="78"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="81"/>
     </row>
     <row r="13" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="80"/>
+      <c r="A13" s="83"/>
       <c r="B13" s="21" t="s">
         <v>152</v>
       </c>
@@ -2303,24 +2324,24 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="79" t="s">
+      <c r="A14" s="82" t="s">
         <v>148</v>
       </c>
-      <c r="B14" s="77" t="s">
+      <c r="B14" s="80" t="s">
         <v>167</v>
       </c>
-      <c r="C14" s="77"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77" t="s">
+      <c r="C14" s="80"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="80" t="s">
         <v>168</v>
       </c>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="78"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="81"/>
     </row>
     <row r="15" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="75"/>
+      <c r="A15" s="78"/>
       <c r="B15" s="19" t="s">
         <v>152</v>
       </c>
@@ -2347,26 +2368,26 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="74" t="s">
+      <c r="A16" s="77" t="s">
         <v>147</v>
       </c>
-      <c r="B16" s="72" t="s">
+      <c r="B16" s="75" t="s">
         <v>166</v>
       </c>
-      <c r="C16" s="72"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="72" t="s">
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="75" t="s">
         <v>149</v>
       </c>
-      <c r="G16" s="72"/>
-      <c r="H16" s="72"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
       <c r="I16" s="25" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="75"/>
+      <c r="A17" s="78"/>
       <c r="B17" s="19" t="s">
         <v>152</v>
       </c>
@@ -2393,22 +2414,22 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="74">
+      <c r="A18" s="77">
         <v>580</v>
       </c>
-      <c r="B18" s="72" t="s">
+      <c r="B18" s="75" t="s">
         <v>129</v>
       </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="73"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="75"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="76"/>
     </row>
     <row r="19" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="75"/>
+      <c r="A19" s="78"/>
       <c r="B19" s="23" t="s">
         <v>130</v>
       </c>
@@ -2435,22 +2456,22 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="79" t="s">
+      <c r="A20" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="77" t="s">
+      <c r="B20" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="C20" s="77"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="78"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="81"/>
     </row>
     <row r="21" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="75"/>
+      <c r="A21" s="78"/>
       <c r="B21" s="23" t="s">
         <v>130</v>
       </c>
@@ -2477,24 +2498,24 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="74" t="s">
+      <c r="A22" s="77" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="72" t="s">
+      <c r="B22" s="75" t="s">
         <v>145</v>
       </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72" t="s">
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="75" t="s">
         <v>146</v>
       </c>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="73"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
+      <c r="I22" s="76"/>
     </row>
     <row r="23" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="75"/>
+      <c r="A23" s="78"/>
       <c r="B23" s="19" t="s">
         <v>152</v>
       </c>
@@ -2521,24 +2542,24 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="74" t="s">
+      <c r="A24" s="77" t="s">
         <v>157</v>
       </c>
-      <c r="B24" s="72" t="s">
+      <c r="B24" s="75" t="s">
         <v>164</v>
       </c>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72" t="s">
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75" t="s">
         <v>165</v>
       </c>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="73"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="76"/>
     </row>
     <row r="25" spans="1:9" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="75"/>
+      <c r="A25" s="78"/>
       <c r="B25" s="19" t="s">
         <v>152</v>
       </c>
@@ -2616,42 +2637,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="88" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-      <c r="S1" s="85"/>
-      <c r="T1" s="85"/>
-      <c r="U1" s="85"/>
-      <c r="V1" s="85"/>
-      <c r="W1" s="85"/>
-      <c r="X1" s="85"/>
-      <c r="Y1" s="85"/>
-      <c r="Z1" s="85"/>
-      <c r="AA1" s="85"/>
-      <c r="AB1" s="85"/>
-      <c r="AC1" s="85"/>
-      <c r="AD1" s="85"/>
-      <c r="AE1" s="85"/>
-      <c r="AF1" s="85"/>
-      <c r="AG1" s="85"/>
-      <c r="AH1" s="85"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
+      <c r="V1" s="88"/>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="88"/>
+      <c r="Z1" s="88"/>
+      <c r="AA1" s="88"/>
+      <c r="AB1" s="88"/>
+      <c r="AC1" s="88"/>
+      <c r="AD1" s="88"/>
+      <c r="AE1" s="88"/>
+      <c r="AF1" s="88"/>
+      <c r="AG1" s="88"/>
+      <c r="AH1" s="88"/>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C2" s="1">
@@ -3310,14 +3331,14 @@
       <c r="B11" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="93" t="s">
+      <c r="C11" s="96" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="94"/>
-      <c r="E11" s="93" t="s">
+      <c r="D11" s="97"/>
+      <c r="E11" s="96" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="94"/>
+      <c r="F11" s="97"/>
       <c r="G11" s="9" t="s">
         <v>64</v>
       </c>
@@ -3330,14 +3351,14 @@
       <c r="J11" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K11" s="93" t="s">
+      <c r="K11" s="96" t="s">
         <v>66</v>
       </c>
-      <c r="L11" s="94"/>
-      <c r="M11" s="93" t="s">
+      <c r="L11" s="97"/>
+      <c r="M11" s="96" t="s">
         <v>67</v>
       </c>
-      <c r="N11" s="94"/>
+      <c r="N11" s="97"/>
       <c r="O11" s="3" t="s">
         <v>12</v>
       </c>
@@ -3443,60 +3464,60 @@
       <c r="C13" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="88" t="s">
+      <c r="D13" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="88"/>
-      <c r="F13" s="88" t="s">
+      <c r="E13" s="91"/>
+      <c r="F13" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="88"/>
-      <c r="H13" s="88"/>
-      <c r="I13" s="88" t="s">
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="J13" s="88"/>
-      <c r="K13" s="88" t="s">
+      <c r="J13" s="91"/>
+      <c r="K13" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="88"/>
-      <c r="M13" s="88" t="s">
+      <c r="L13" s="91"/>
+      <c r="M13" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="N13" s="88"/>
-      <c r="O13" s="88"/>
-      <c r="P13" s="88"/>
-      <c r="Q13" s="88"/>
+      <c r="N13" s="91"/>
+      <c r="O13" s="91"/>
+      <c r="P13" s="91"/>
+      <c r="Q13" s="91"/>
       <c r="R13" s="27" t="s">
         <v>51</v>
       </c>
       <c r="S13" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="T13" s="88" t="s">
+      <c r="T13" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="U13" s="88"/>
-      <c r="V13" s="88" t="s">
+      <c r="U13" s="91"/>
+      <c r="V13" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="W13" s="88"/>
-      <c r="X13" s="88"/>
-      <c r="Y13" s="88" t="s">
+      <c r="W13" s="91"/>
+      <c r="X13" s="91"/>
+      <c r="Y13" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="Z13" s="88"/>
-      <c r="AA13" s="88" t="s">
+      <c r="Z13" s="91"/>
+      <c r="AA13" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="AB13" s="88"/>
-      <c r="AC13" s="88" t="s">
+      <c r="AB13" s="91"/>
+      <c r="AC13" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="AD13" s="88"/>
-      <c r="AE13" s="88"/>
-      <c r="AF13" s="88"/>
-      <c r="AG13" s="88"/>
+      <c r="AD13" s="91"/>
+      <c r="AE13" s="91"/>
+      <c r="AF13" s="91"/>
+      <c r="AG13" s="91"/>
       <c r="AH13" s="27" t="s">
         <v>51</v>
       </c>
@@ -3536,104 +3557,104 @@
       <c r="AH14" s="6"/>
     </row>
     <row r="15" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="92" t="s">
+      <c r="A15" s="95" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="91" t="s">
+      <c r="B15" s="94" t="s">
         <v>197</v>
       </c>
-      <c r="C15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="J15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="K15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="L15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="M15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="N15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="O15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="P15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="R15" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="S15" s="83" t="s">
+      <c r="C15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="M15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="N15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="O15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="P15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="R15" s="93" t="s">
+        <v>12</v>
+      </c>
+      <c r="S15" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="T15" s="82"/>
-      <c r="U15" s="82"/>
-      <c r="V15" s="84"/>
-      <c r="W15" s="83" t="s">
+      <c r="T15" s="85"/>
+      <c r="U15" s="85"/>
+      <c r="V15" s="87"/>
+      <c r="W15" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="X15" s="82"/>
-      <c r="Y15" s="82"/>
-      <c r="Z15" s="84"/>
-      <c r="AA15" s="83" t="s">
+      <c r="X15" s="85"/>
+      <c r="Y15" s="85"/>
+      <c r="Z15" s="87"/>
+      <c r="AA15" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="AB15" s="82"/>
-      <c r="AC15" s="82"/>
-      <c r="AD15" s="84"/>
-      <c r="AE15" s="83" t="s">
+      <c r="AB15" s="85"/>
+      <c r="AC15" s="85"/>
+      <c r="AD15" s="87"/>
+      <c r="AE15" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="AF15" s="82"/>
-      <c r="AG15" s="82"/>
-      <c r="AH15" s="84"/>
+      <c r="AF15" s="85"/>
+      <c r="AG15" s="85"/>
+      <c r="AH15" s="87"/>
     </row>
     <row r="16" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="92"/>
-      <c r="B16" s="91"/>
-      <c r="C16" s="90"/>
-      <c r="D16" s="90"/>
-      <c r="E16" s="90"/>
-      <c r="F16" s="90"/>
-      <c r="G16" s="90"/>
-      <c r="H16" s="90"/>
-      <c r="I16" s="90"/>
-      <c r="J16" s="90"/>
-      <c r="K16" s="90"/>
-      <c r="L16" s="90"/>
-      <c r="M16" s="90"/>
-      <c r="N16" s="90"/>
-      <c r="O16" s="90"/>
-      <c r="P16" s="90"/>
-      <c r="Q16" s="90"/>
-      <c r="R16" s="90"/>
+      <c r="A16" s="95"/>
+      <c r="B16" s="94"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93"/>
+      <c r="J16" s="93"/>
+      <c r="K16" s="93"/>
+      <c r="L16" s="93"/>
+      <c r="M16" s="93"/>
+      <c r="N16" s="93"/>
+      <c r="O16" s="93"/>
+      <c r="P16" s="93"/>
+      <c r="Q16" s="93"/>
+      <c r="R16" s="93"/>
       <c r="S16" s="3">
         <v>0</v>
       </c>
@@ -3705,19 +3726,19 @@
       <c r="G18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H18" s="88" t="s">
+      <c r="H18" s="91" t="s">
         <v>75</v>
       </c>
-      <c r="I18" s="88"/>
-      <c r="J18" s="88"/>
-      <c r="K18" s="88"/>
-      <c r="L18" s="88"/>
-      <c r="M18" s="88"/>
-      <c r="N18" s="88"/>
-      <c r="O18" s="88"/>
-      <c r="P18" s="88"/>
-      <c r="Q18" s="88"/>
-      <c r="R18" s="88"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="91"/>
+      <c r="K18" s="91"/>
+      <c r="L18" s="91"/>
+      <c r="M18" s="91"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="91"/>
+      <c r="Q18" s="91"/>
+      <c r="R18" s="91"/>
       <c r="S18" s="3" t="s">
         <v>12</v>
       </c>
@@ -3733,19 +3754,19 @@
       <c r="W18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="X18" s="88" t="s">
+      <c r="X18" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="Y18" s="88"/>
-      <c r="Z18" s="88"/>
-      <c r="AA18" s="88"/>
-      <c r="AB18" s="88"/>
-      <c r="AC18" s="88"/>
-      <c r="AD18" s="88"/>
-      <c r="AE18" s="88"/>
-      <c r="AF18" s="88"/>
-      <c r="AG18" s="88"/>
-      <c r="AH18" s="88"/>
+      <c r="Y18" s="91"/>
+      <c r="Z18" s="91"/>
+      <c r="AA18" s="91"/>
+      <c r="AB18" s="91"/>
+      <c r="AC18" s="91"/>
+      <c r="AD18" s="91"/>
+      <c r="AE18" s="91"/>
+      <c r="AF18" s="91"/>
+      <c r="AG18" s="91"/>
+      <c r="AH18" s="91"/>
     </row>
     <row r="19" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="20" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3779,32 +3800,32 @@
       <c r="J20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K20" s="83" t="s">
+      <c r="K20" s="86" t="s">
         <v>78</v>
       </c>
-      <c r="L20" s="82"/>
-      <c r="M20" s="82"/>
-      <c r="N20" s="82"/>
-      <c r="O20" s="82"/>
-      <c r="P20" s="82"/>
-      <c r="Q20" s="82"/>
-      <c r="R20" s="82"/>
-      <c r="S20" s="82"/>
-      <c r="T20" s="82"/>
-      <c r="U20" s="82"/>
-      <c r="V20" s="82"/>
-      <c r="W20" s="82"/>
-      <c r="X20" s="82"/>
-      <c r="Y20" s="82"/>
-      <c r="Z20" s="82"/>
-      <c r="AA20" s="82"/>
-      <c r="AB20" s="82"/>
-      <c r="AC20" s="82"/>
-      <c r="AD20" s="82"/>
-      <c r="AE20" s="82"/>
-      <c r="AF20" s="82"/>
-      <c r="AG20" s="82"/>
-      <c r="AH20" s="84"/>
+      <c r="L20" s="85"/>
+      <c r="M20" s="85"/>
+      <c r="N20" s="85"/>
+      <c r="O20" s="85"/>
+      <c r="P20" s="85"/>
+      <c r="Q20" s="85"/>
+      <c r="R20" s="85"/>
+      <c r="S20" s="85"/>
+      <c r="T20" s="85"/>
+      <c r="U20" s="85"/>
+      <c r="V20" s="85"/>
+      <c r="W20" s="85"/>
+      <c r="X20" s="85"/>
+      <c r="Y20" s="85"/>
+      <c r="Z20" s="85"/>
+      <c r="AA20" s="85"/>
+      <c r="AB20" s="85"/>
+      <c r="AC20" s="85"/>
+      <c r="AD20" s="85"/>
+      <c r="AE20" s="85"/>
+      <c r="AF20" s="85"/>
+      <c r="AG20" s="85"/>
+      <c r="AH20" s="87"/>
     </row>
     <row r="21" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3838,32 +3859,32 @@
       <c r="J22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K22" s="83" t="s">
+      <c r="K22" s="86" t="s">
         <v>78</v>
       </c>
-      <c r="L22" s="82"/>
-      <c r="M22" s="82"/>
-      <c r="N22" s="82"/>
-      <c r="O22" s="82"/>
-      <c r="P22" s="82"/>
-      <c r="Q22" s="82"/>
-      <c r="R22" s="82"/>
-      <c r="S22" s="82"/>
-      <c r="T22" s="82"/>
-      <c r="U22" s="82"/>
-      <c r="V22" s="82"/>
-      <c r="W22" s="82"/>
-      <c r="X22" s="82"/>
-      <c r="Y22" s="82"/>
-      <c r="Z22" s="82"/>
-      <c r="AA22" s="82"/>
-      <c r="AB22" s="82"/>
-      <c r="AC22" s="82"/>
-      <c r="AD22" s="82"/>
-      <c r="AE22" s="82"/>
-      <c r="AF22" s="82"/>
-      <c r="AG22" s="82"/>
-      <c r="AH22" s="84"/>
+      <c r="L22" s="85"/>
+      <c r="M22" s="85"/>
+      <c r="N22" s="85"/>
+      <c r="O22" s="85"/>
+      <c r="P22" s="85"/>
+      <c r="Q22" s="85"/>
+      <c r="R22" s="85"/>
+      <c r="S22" s="85"/>
+      <c r="T22" s="85"/>
+      <c r="U22" s="85"/>
+      <c r="V22" s="85"/>
+      <c r="W22" s="85"/>
+      <c r="X22" s="85"/>
+      <c r="Y22" s="85"/>
+      <c r="Z22" s="85"/>
+      <c r="AA22" s="85"/>
+      <c r="AB22" s="85"/>
+      <c r="AC22" s="85"/>
+      <c r="AD22" s="85"/>
+      <c r="AE22" s="85"/>
+      <c r="AF22" s="85"/>
+      <c r="AG22" s="85"/>
+      <c r="AH22" s="87"/>
     </row>
     <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3873,42 +3894,42 @@
       <c r="B24" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="C24" s="88" t="s">
+      <c r="C24" s="91" t="s">
         <v>209</v>
       </c>
-      <c r="D24" s="88"/>
-      <c r="E24" s="88"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="88"/>
-      <c r="I24" s="88"/>
-      <c r="J24" s="88"/>
-      <c r="K24" s="88"/>
-      <c r="L24" s="88"/>
-      <c r="M24" s="88"/>
-      <c r="N24" s="88"/>
-      <c r="O24" s="88"/>
-      <c r="P24" s="88"/>
-      <c r="Q24" s="88"/>
-      <c r="R24" s="88"/>
-      <c r="S24" s="88" t="s">
+      <c r="D24" s="91"/>
+      <c r="E24" s="91"/>
+      <c r="F24" s="91"/>
+      <c r="G24" s="91"/>
+      <c r="H24" s="91"/>
+      <c r="I24" s="91"/>
+      <c r="J24" s="91"/>
+      <c r="K24" s="91"/>
+      <c r="L24" s="91"/>
+      <c r="M24" s="91"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="91"/>
+      <c r="P24" s="91"/>
+      <c r="Q24" s="91"/>
+      <c r="R24" s="91"/>
+      <c r="S24" s="91" t="s">
         <v>210</v>
       </c>
-      <c r="T24" s="88"/>
-      <c r="U24" s="88"/>
-      <c r="V24" s="88"/>
-      <c r="W24" s="88"/>
-      <c r="X24" s="88"/>
-      <c r="Y24" s="88"/>
-      <c r="Z24" s="88"/>
-      <c r="AA24" s="88"/>
-      <c r="AB24" s="88"/>
-      <c r="AC24" s="88"/>
-      <c r="AD24" s="88"/>
-      <c r="AE24" s="88"/>
-      <c r="AF24" s="88"/>
-      <c r="AG24" s="88"/>
-      <c r="AH24" s="88"/>
+      <c r="T24" s="91"/>
+      <c r="U24" s="91"/>
+      <c r="V24" s="91"/>
+      <c r="W24" s="91"/>
+      <c r="X24" s="91"/>
+      <c r="Y24" s="91"/>
+      <c r="Z24" s="91"/>
+      <c r="AA24" s="91"/>
+      <c r="AB24" s="91"/>
+      <c r="AC24" s="91"/>
+      <c r="AD24" s="91"/>
+      <c r="AE24" s="91"/>
+      <c r="AF24" s="91"/>
+      <c r="AG24" s="91"/>
+      <c r="AH24" s="91"/>
     </row>
     <row r="26" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
@@ -3917,42 +3938,42 @@
       <c r="B26" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="C26" s="88" t="s">
+      <c r="C26" s="91" t="s">
         <v>217</v>
       </c>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="88"/>
-      <c r="H26" s="88"/>
-      <c r="I26" s="88"/>
-      <c r="J26" s="88"/>
-      <c r="K26" s="88"/>
-      <c r="L26" s="88"/>
-      <c r="M26" s="88"/>
-      <c r="N26" s="88"/>
-      <c r="O26" s="88"/>
-      <c r="P26" s="88"/>
-      <c r="Q26" s="88"/>
-      <c r="R26" s="88"/>
-      <c r="S26" s="88" t="s">
+      <c r="D26" s="91"/>
+      <c r="E26" s="91"/>
+      <c r="F26" s="91"/>
+      <c r="G26" s="91"/>
+      <c r="H26" s="91"/>
+      <c r="I26" s="91"/>
+      <c r="J26" s="91"/>
+      <c r="K26" s="91"/>
+      <c r="L26" s="91"/>
+      <c r="M26" s="91"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="91"/>
+      <c r="P26" s="91"/>
+      <c r="Q26" s="91"/>
+      <c r="R26" s="91"/>
+      <c r="S26" s="91" t="s">
         <v>224</v>
       </c>
-      <c r="T26" s="88"/>
-      <c r="U26" s="88"/>
-      <c r="V26" s="88"/>
-      <c r="W26" s="88"/>
-      <c r="X26" s="88"/>
-      <c r="Y26" s="88"/>
-      <c r="Z26" s="88"/>
-      <c r="AA26" s="88"/>
-      <c r="AB26" s="88"/>
-      <c r="AC26" s="88"/>
-      <c r="AD26" s="88"/>
-      <c r="AE26" s="88"/>
-      <c r="AF26" s="88"/>
-      <c r="AG26" s="88"/>
-      <c r="AH26" s="88"/>
+      <c r="T26" s="91"/>
+      <c r="U26" s="91"/>
+      <c r="V26" s="91"/>
+      <c r="W26" s="91"/>
+      <c r="X26" s="91"/>
+      <c r="Y26" s="91"/>
+      <c r="Z26" s="91"/>
+      <c r="AA26" s="91"/>
+      <c r="AB26" s="91"/>
+      <c r="AC26" s="91"/>
+      <c r="AD26" s="91"/>
+      <c r="AE26" s="91"/>
+      <c r="AF26" s="91"/>
+      <c r="AG26" s="91"/>
+      <c r="AH26" s="91"/>
     </row>
     <row r="27" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3962,42 +3983,42 @@
       <c r="B28" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="C28" s="88" t="s">
+      <c r="C28" s="91" t="s">
         <v>214</v>
       </c>
-      <c r="D28" s="88"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="88"/>
-      <c r="G28" s="88"/>
-      <c r="H28" s="88"/>
-      <c r="I28" s="88"/>
-      <c r="J28" s="88"/>
-      <c r="K28" s="88"/>
-      <c r="L28" s="88"/>
-      <c r="M28" s="88"/>
-      <c r="N28" s="88"/>
-      <c r="O28" s="88"/>
-      <c r="P28" s="88"/>
-      <c r="Q28" s="88"/>
-      <c r="R28" s="88"/>
-      <c r="S28" s="88" t="s">
+      <c r="D28" s="91"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="91"/>
+      <c r="H28" s="91"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="91"/>
+      <c r="K28" s="91"/>
+      <c r="L28" s="91"/>
+      <c r="M28" s="91"/>
+      <c r="N28" s="91"/>
+      <c r="O28" s="91"/>
+      <c r="P28" s="91"/>
+      <c r="Q28" s="91"/>
+      <c r="R28" s="91"/>
+      <c r="S28" s="91" t="s">
         <v>211</v>
       </c>
-      <c r="T28" s="88"/>
-      <c r="U28" s="88"/>
-      <c r="V28" s="88"/>
-      <c r="W28" s="88"/>
-      <c r="X28" s="88"/>
-      <c r="Y28" s="88"/>
-      <c r="Z28" s="88"/>
-      <c r="AA28" s="88"/>
-      <c r="AB28" s="88"/>
-      <c r="AC28" s="88"/>
-      <c r="AD28" s="88"/>
-      <c r="AE28" s="88"/>
-      <c r="AF28" s="88"/>
-      <c r="AG28" s="88"/>
-      <c r="AH28" s="88"/>
+      <c r="T28" s="91"/>
+      <c r="U28" s="91"/>
+      <c r="V28" s="91"/>
+      <c r="W28" s="91"/>
+      <c r="X28" s="91"/>
+      <c r="Y28" s="91"/>
+      <c r="Z28" s="91"/>
+      <c r="AA28" s="91"/>
+      <c r="AB28" s="91"/>
+      <c r="AC28" s="91"/>
+      <c r="AD28" s="91"/>
+      <c r="AE28" s="91"/>
+      <c r="AF28" s="91"/>
+      <c r="AG28" s="91"/>
+      <c r="AH28" s="91"/>
     </row>
     <row r="30" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
@@ -4006,42 +4027,42 @@
       <c r="B30" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="C30" s="88" t="s">
+      <c r="C30" s="91" t="s">
         <v>218</v>
       </c>
-      <c r="D30" s="88"/>
-      <c r="E30" s="88"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="88"/>
-      <c r="H30" s="88"/>
-      <c r="I30" s="88"/>
-      <c r="J30" s="88"/>
-      <c r="K30" s="88"/>
-      <c r="L30" s="88"/>
-      <c r="M30" s="88"/>
-      <c r="N30" s="88"/>
-      <c r="O30" s="88"/>
-      <c r="P30" s="88"/>
-      <c r="Q30" s="88"/>
-      <c r="R30" s="88"/>
-      <c r="S30" s="88" t="s">
+      <c r="D30" s="91"/>
+      <c r="E30" s="91"/>
+      <c r="F30" s="91"/>
+      <c r="G30" s="91"/>
+      <c r="H30" s="91"/>
+      <c r="I30" s="91"/>
+      <c r="J30" s="91"/>
+      <c r="K30" s="91"/>
+      <c r="L30" s="91"/>
+      <c r="M30" s="91"/>
+      <c r="N30" s="91"/>
+      <c r="O30" s="91"/>
+      <c r="P30" s="91"/>
+      <c r="Q30" s="91"/>
+      <c r="R30" s="91"/>
+      <c r="S30" s="91" t="s">
         <v>223</v>
       </c>
-      <c r="T30" s="88"/>
-      <c r="U30" s="88"/>
-      <c r="V30" s="88"/>
-      <c r="W30" s="88"/>
-      <c r="X30" s="88"/>
-      <c r="Y30" s="88"/>
-      <c r="Z30" s="88"/>
-      <c r="AA30" s="88"/>
-      <c r="AB30" s="88"/>
-      <c r="AC30" s="88"/>
-      <c r="AD30" s="88"/>
-      <c r="AE30" s="88"/>
-      <c r="AF30" s="88"/>
-      <c r="AG30" s="88"/>
-      <c r="AH30" s="88"/>
+      <c r="T30" s="91"/>
+      <c r="U30" s="91"/>
+      <c r="V30" s="91"/>
+      <c r="W30" s="91"/>
+      <c r="X30" s="91"/>
+      <c r="Y30" s="91"/>
+      <c r="Z30" s="91"/>
+      <c r="AA30" s="91"/>
+      <c r="AB30" s="91"/>
+      <c r="AC30" s="91"/>
+      <c r="AD30" s="91"/>
+      <c r="AE30" s="91"/>
+      <c r="AF30" s="91"/>
+      <c r="AG30" s="91"/>
+      <c r="AH30" s="91"/>
     </row>
     <row r="31" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4051,42 +4072,42 @@
       <c r="B32" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="C32" s="88" t="s">
+      <c r="C32" s="91" t="s">
         <v>215</v>
       </c>
-      <c r="D32" s="88"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="88"/>
-      <c r="G32" s="88"/>
-      <c r="H32" s="88"/>
-      <c r="I32" s="88"/>
-      <c r="J32" s="88"/>
-      <c r="K32" s="88"/>
-      <c r="L32" s="88"/>
-      <c r="M32" s="88"/>
-      <c r="N32" s="88"/>
-      <c r="O32" s="88"/>
-      <c r="P32" s="88"/>
-      <c r="Q32" s="88"/>
-      <c r="R32" s="88"/>
-      <c r="S32" s="88" t="s">
+      <c r="D32" s="91"/>
+      <c r="E32" s="91"/>
+      <c r="F32" s="91"/>
+      <c r="G32" s="91"/>
+      <c r="H32" s="91"/>
+      <c r="I32" s="91"/>
+      <c r="J32" s="91"/>
+      <c r="K32" s="91"/>
+      <c r="L32" s="91"/>
+      <c r="M32" s="91"/>
+      <c r="N32" s="91"/>
+      <c r="O32" s="91"/>
+      <c r="P32" s="91"/>
+      <c r="Q32" s="91"/>
+      <c r="R32" s="91"/>
+      <c r="S32" s="91" t="s">
         <v>212</v>
       </c>
-      <c r="T32" s="88"/>
-      <c r="U32" s="88"/>
-      <c r="V32" s="88"/>
-      <c r="W32" s="88"/>
-      <c r="X32" s="88"/>
-      <c r="Y32" s="88"/>
-      <c r="Z32" s="88"/>
-      <c r="AA32" s="88"/>
-      <c r="AB32" s="88"/>
-      <c r="AC32" s="88"/>
-      <c r="AD32" s="88"/>
-      <c r="AE32" s="88"/>
-      <c r="AF32" s="88"/>
-      <c r="AG32" s="88"/>
-      <c r="AH32" s="88"/>
+      <c r="T32" s="91"/>
+      <c r="U32" s="91"/>
+      <c r="V32" s="91"/>
+      <c r="W32" s="91"/>
+      <c r="X32" s="91"/>
+      <c r="Y32" s="91"/>
+      <c r="Z32" s="91"/>
+      <c r="AA32" s="91"/>
+      <c r="AB32" s="91"/>
+      <c r="AC32" s="91"/>
+      <c r="AD32" s="91"/>
+      <c r="AE32" s="91"/>
+      <c r="AF32" s="91"/>
+      <c r="AG32" s="91"/>
+      <c r="AH32" s="91"/>
     </row>
     <row r="34" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
@@ -4095,42 +4116,42 @@
       <c r="B34" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="C34" s="88" t="s">
+      <c r="C34" s="91" t="s">
         <v>219</v>
       </c>
-      <c r="D34" s="88"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="88"/>
-      <c r="G34" s="88"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="88"/>
-      <c r="J34" s="88"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="88"/>
-      <c r="M34" s="88"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="88"/>
-      <c r="P34" s="88"/>
-      <c r="Q34" s="88"/>
-      <c r="R34" s="88"/>
-      <c r="S34" s="88" t="s">
+      <c r="D34" s="91"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="91"/>
+      <c r="G34" s="91"/>
+      <c r="H34" s="91"/>
+      <c r="I34" s="91"/>
+      <c r="J34" s="91"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="91"/>
+      <c r="M34" s="91"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="91"/>
+      <c r="P34" s="91"/>
+      <c r="Q34" s="91"/>
+      <c r="R34" s="91"/>
+      <c r="S34" s="91" t="s">
         <v>222</v>
       </c>
-      <c r="T34" s="88"/>
-      <c r="U34" s="88"/>
-      <c r="V34" s="88"/>
-      <c r="W34" s="88"/>
-      <c r="X34" s="88"/>
-      <c r="Y34" s="88"/>
-      <c r="Z34" s="88"/>
-      <c r="AA34" s="88"/>
-      <c r="AB34" s="88"/>
-      <c r="AC34" s="88"/>
-      <c r="AD34" s="88"/>
-      <c r="AE34" s="88"/>
-      <c r="AF34" s="88"/>
-      <c r="AG34" s="88"/>
-      <c r="AH34" s="88"/>
+      <c r="T34" s="91"/>
+      <c r="U34" s="91"/>
+      <c r="V34" s="91"/>
+      <c r="W34" s="91"/>
+      <c r="X34" s="91"/>
+      <c r="Y34" s="91"/>
+      <c r="Z34" s="91"/>
+      <c r="AA34" s="91"/>
+      <c r="AB34" s="91"/>
+      <c r="AC34" s="91"/>
+      <c r="AD34" s="91"/>
+      <c r="AE34" s="91"/>
+      <c r="AF34" s="91"/>
+      <c r="AG34" s="91"/>
+      <c r="AH34" s="91"/>
     </row>
     <row r="35" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4140,42 +4161,42 @@
       <c r="B36" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="C36" s="88" t="s">
+      <c r="C36" s="91" t="s">
         <v>216</v>
       </c>
-      <c r="D36" s="88"/>
-      <c r="E36" s="88"/>
-      <c r="F36" s="88"/>
-      <c r="G36" s="88"/>
-      <c r="H36" s="88"/>
-      <c r="I36" s="88"/>
-      <c r="J36" s="88"/>
-      <c r="K36" s="88"/>
-      <c r="L36" s="88"/>
-      <c r="M36" s="88"/>
-      <c r="N36" s="88"/>
-      <c r="O36" s="88"/>
-      <c r="P36" s="88"/>
-      <c r="Q36" s="88"/>
-      <c r="R36" s="88"/>
-      <c r="S36" s="88" t="s">
+      <c r="D36" s="91"/>
+      <c r="E36" s="91"/>
+      <c r="F36" s="91"/>
+      <c r="G36" s="91"/>
+      <c r="H36" s="91"/>
+      <c r="I36" s="91"/>
+      <c r="J36" s="91"/>
+      <c r="K36" s="91"/>
+      <c r="L36" s="91"/>
+      <c r="M36" s="91"/>
+      <c r="N36" s="91"/>
+      <c r="O36" s="91"/>
+      <c r="P36" s="91"/>
+      <c r="Q36" s="91"/>
+      <c r="R36" s="91"/>
+      <c r="S36" s="91" t="s">
         <v>213</v>
       </c>
-      <c r="T36" s="88"/>
-      <c r="U36" s="88"/>
-      <c r="V36" s="88"/>
-      <c r="W36" s="88"/>
-      <c r="X36" s="88"/>
-      <c r="Y36" s="88"/>
-      <c r="Z36" s="88"/>
-      <c r="AA36" s="88"/>
-      <c r="AB36" s="88"/>
-      <c r="AC36" s="88"/>
-      <c r="AD36" s="88"/>
-      <c r="AE36" s="88"/>
-      <c r="AF36" s="88"/>
-      <c r="AG36" s="88"/>
-      <c r="AH36" s="88"/>
+      <c r="T36" s="91"/>
+      <c r="U36" s="91"/>
+      <c r="V36" s="91"/>
+      <c r="W36" s="91"/>
+      <c r="X36" s="91"/>
+      <c r="Y36" s="91"/>
+      <c r="Z36" s="91"/>
+      <c r="AA36" s="91"/>
+      <c r="AB36" s="91"/>
+      <c r="AC36" s="91"/>
+      <c r="AD36" s="91"/>
+      <c r="AE36" s="91"/>
+      <c r="AF36" s="91"/>
+      <c r="AG36" s="91"/>
+      <c r="AH36" s="91"/>
     </row>
     <row r="38" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
@@ -4184,82 +4205,82 @@
       <c r="B38" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="C38" s="88" t="s">
+      <c r="C38" s="91" t="s">
         <v>220</v>
       </c>
-      <c r="D38" s="88"/>
-      <c r="E38" s="88"/>
-      <c r="F38" s="88"/>
-      <c r="G38" s="88"/>
-      <c r="H38" s="88"/>
-      <c r="I38" s="88"/>
-      <c r="J38" s="88"/>
-      <c r="K38" s="88"/>
-      <c r="L38" s="88"/>
-      <c r="M38" s="88"/>
-      <c r="N38" s="88"/>
-      <c r="O38" s="88"/>
-      <c r="P38" s="88"/>
-      <c r="Q38" s="88"/>
-      <c r="R38" s="88"/>
-      <c r="S38" s="88" t="s">
+      <c r="D38" s="91"/>
+      <c r="E38" s="91"/>
+      <c r="F38" s="91"/>
+      <c r="G38" s="91"/>
+      <c r="H38" s="91"/>
+      <c r="I38" s="91"/>
+      <c r="J38" s="91"/>
+      <c r="K38" s="91"/>
+      <c r="L38" s="91"/>
+      <c r="M38" s="91"/>
+      <c r="N38" s="91"/>
+      <c r="O38" s="91"/>
+      <c r="P38" s="91"/>
+      <c r="Q38" s="91"/>
+      <c r="R38" s="91"/>
+      <c r="S38" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="T38" s="88"/>
-      <c r="U38" s="88"/>
-      <c r="V38" s="88"/>
-      <c r="W38" s="88"/>
-      <c r="X38" s="88"/>
-      <c r="Y38" s="88"/>
-      <c r="Z38" s="88"/>
-      <c r="AA38" s="88"/>
-      <c r="AB38" s="88"/>
-      <c r="AC38" s="88"/>
-      <c r="AD38" s="88"/>
-      <c r="AE38" s="88"/>
-      <c r="AF38" s="88"/>
-      <c r="AG38" s="88"/>
-      <c r="AH38" s="88"/>
+      <c r="T38" s="91"/>
+      <c r="U38" s="91"/>
+      <c r="V38" s="91"/>
+      <c r="W38" s="91"/>
+      <c r="X38" s="91"/>
+      <c r="Y38" s="91"/>
+      <c r="Z38" s="91"/>
+      <c r="AA38" s="91"/>
+      <c r="AB38" s="91"/>
+      <c r="AC38" s="91"/>
+      <c r="AD38" s="91"/>
+      <c r="AE38" s="91"/>
+      <c r="AF38" s="91"/>
+      <c r="AG38" s="91"/>
+      <c r="AH38" s="91"/>
     </row>
     <row r="39" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="41" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="85" t="s">
+      <c r="A41" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="B41" s="85"/>
-      <c r="C41" s="85"/>
-      <c r="D41" s="85"/>
-      <c r="E41" s="85"/>
-      <c r="F41" s="85"/>
-      <c r="G41" s="85"/>
-      <c r="H41" s="85"/>
-      <c r="I41" s="85"/>
-      <c r="J41" s="85"/>
-      <c r="K41" s="85"/>
-      <c r="L41" s="85"/>
-      <c r="M41" s="85"/>
-      <c r="N41" s="85"/>
-      <c r="O41" s="85"/>
-      <c r="P41" s="85"/>
-      <c r="Q41" s="85"/>
-      <c r="R41" s="85"/>
-      <c r="S41" s="85"/>
-      <c r="T41" s="85"/>
-      <c r="U41" s="85"/>
-      <c r="V41" s="85"/>
-      <c r="W41" s="85"/>
-      <c r="X41" s="85"/>
-      <c r="Y41" s="85"/>
-      <c r="Z41" s="85"/>
-      <c r="AA41" s="85"/>
-      <c r="AB41" s="85"/>
-      <c r="AC41" s="85"/>
-      <c r="AD41" s="85"/>
-      <c r="AE41" s="85"/>
-      <c r="AF41" s="85"/>
-      <c r="AG41" s="85"/>
-      <c r="AH41" s="85"/>
+      <c r="B41" s="88"/>
+      <c r="C41" s="88"/>
+      <c r="D41" s="88"/>
+      <c r="E41" s="88"/>
+      <c r="F41" s="88"/>
+      <c r="G41" s="88"/>
+      <c r="H41" s="88"/>
+      <c r="I41" s="88"/>
+      <c r="J41" s="88"/>
+      <c r="K41" s="88"/>
+      <c r="L41" s="88"/>
+      <c r="M41" s="88"/>
+      <c r="N41" s="88"/>
+      <c r="O41" s="88"/>
+      <c r="P41" s="88"/>
+      <c r="Q41" s="88"/>
+      <c r="R41" s="88"/>
+      <c r="S41" s="88"/>
+      <c r="T41" s="88"/>
+      <c r="U41" s="88"/>
+      <c r="V41" s="88"/>
+      <c r="W41" s="88"/>
+      <c r="X41" s="88"/>
+      <c r="Y41" s="88"/>
+      <c r="Z41" s="88"/>
+      <c r="AA41" s="88"/>
+      <c r="AB41" s="88"/>
+      <c r="AC41" s="88"/>
+      <c r="AD41" s="88"/>
+      <c r="AE41" s="88"/>
+      <c r="AF41" s="88"/>
+      <c r="AG41" s="88"/>
+      <c r="AH41" s="88"/>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.25">
       <c r="C42" s="1">
@@ -4435,10 +4456,10 @@
       <c r="Y43" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="Z43" s="88" t="s">
+      <c r="Z43" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="AA43" s="88"/>
+      <c r="AA43" s="91"/>
       <c r="AB43" s="10" t="s">
         <v>24</v>
       </c>
@@ -4448,12 +4469,12 @@
       <c r="AD43" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AE43" s="88" t="s">
+      <c r="AE43" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="AF43" s="88"/>
-      <c r="AG43" s="88"/>
-      <c r="AH43" s="88"/>
+      <c r="AF43" s="91"/>
+      <c r="AG43" s="91"/>
+      <c r="AH43" s="91"/>
     </row>
     <row r="45" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
@@ -4486,34 +4507,34 @@
       <c r="J45" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K45" s="83" t="s">
+      <c r="K45" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="L45" s="82"/>
-      <c r="M45" s="82"/>
-      <c r="N45" s="82"/>
-      <c r="O45" s="82"/>
-      <c r="P45" s="82"/>
-      <c r="Q45" s="82"/>
-      <c r="R45" s="82"/>
-      <c r="S45" s="82"/>
-      <c r="T45" s="82"/>
-      <c r="U45" s="82"/>
-      <c r="V45" s="82"/>
-      <c r="W45" s="82"/>
-      <c r="X45" s="82"/>
-      <c r="Y45" s="82"/>
-      <c r="Z45" s="82"/>
-      <c r="AA45" s="82"/>
-      <c r="AB45" s="82"/>
-      <c r="AC45" s="82"/>
-      <c r="AD45" s="82"/>
-      <c r="AE45" s="82"/>
-      <c r="AF45" s="84"/>
-      <c r="AG45" s="86" t="s">
-        <v>12</v>
-      </c>
-      <c r="AH45" s="87"/>
+      <c r="L45" s="85"/>
+      <c r="M45" s="85"/>
+      <c r="N45" s="85"/>
+      <c r="O45" s="85"/>
+      <c r="P45" s="85"/>
+      <c r="Q45" s="85"/>
+      <c r="R45" s="85"/>
+      <c r="S45" s="85"/>
+      <c r="T45" s="85"/>
+      <c r="U45" s="85"/>
+      <c r="V45" s="85"/>
+      <c r="W45" s="85"/>
+      <c r="X45" s="85"/>
+      <c r="Y45" s="85"/>
+      <c r="Z45" s="85"/>
+      <c r="AA45" s="85"/>
+      <c r="AB45" s="85"/>
+      <c r="AC45" s="85"/>
+      <c r="AD45" s="85"/>
+      <c r="AE45" s="85"/>
+      <c r="AF45" s="87"/>
+      <c r="AG45" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH45" s="90"/>
     </row>
     <row r="47" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
@@ -4546,30 +4567,30 @@
       <c r="J47" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K47" s="83" t="s">
+      <c r="K47" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="L47" s="82"/>
-      <c r="M47" s="82"/>
-      <c r="N47" s="82"/>
-      <c r="O47" s="82"/>
-      <c r="P47" s="82"/>
-      <c r="Q47" s="82"/>
-      <c r="R47" s="82"/>
-      <c r="S47" s="82"/>
-      <c r="T47" s="82"/>
-      <c r="U47" s="82"/>
-      <c r="V47" s="82"/>
-      <c r="W47" s="82"/>
-      <c r="X47" s="82"/>
-      <c r="Y47" s="82"/>
-      <c r="Z47" s="82"/>
-      <c r="AA47" s="82"/>
-      <c r="AB47" s="82"/>
-      <c r="AC47" s="82"/>
-      <c r="AD47" s="82"/>
-      <c r="AE47" s="82"/>
-      <c r="AF47" s="82"/>
+      <c r="L47" s="85"/>
+      <c r="M47" s="85"/>
+      <c r="N47" s="85"/>
+      <c r="O47" s="85"/>
+      <c r="P47" s="85"/>
+      <c r="Q47" s="85"/>
+      <c r="R47" s="85"/>
+      <c r="S47" s="85"/>
+      <c r="T47" s="85"/>
+      <c r="U47" s="85"/>
+      <c r="V47" s="85"/>
+      <c r="W47" s="85"/>
+      <c r="X47" s="85"/>
+      <c r="Y47" s="85"/>
+      <c r="Z47" s="85"/>
+      <c r="AA47" s="85"/>
+      <c r="AB47" s="85"/>
+      <c r="AC47" s="85"/>
+      <c r="AD47" s="85"/>
+      <c r="AE47" s="85"/>
+      <c r="AF47" s="85"/>
       <c r="AG47" s="3" t="s">
         <v>12</v>
       </c>
@@ -4608,30 +4629,30 @@
       <c r="J49" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K49" s="83" t="s">
+      <c r="K49" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="L49" s="82"/>
-      <c r="M49" s="82"/>
-      <c r="N49" s="82"/>
-      <c r="O49" s="82"/>
-      <c r="P49" s="82"/>
-      <c r="Q49" s="82"/>
-      <c r="R49" s="82"/>
-      <c r="S49" s="82"/>
-      <c r="T49" s="82"/>
-      <c r="U49" s="82"/>
-      <c r="V49" s="82"/>
-      <c r="W49" s="82"/>
-      <c r="X49" s="82"/>
-      <c r="Y49" s="82"/>
-      <c r="Z49" s="82"/>
-      <c r="AA49" s="82"/>
-      <c r="AB49" s="82"/>
-      <c r="AC49" s="82"/>
-      <c r="AD49" s="82"/>
-      <c r="AE49" s="82"/>
-      <c r="AF49" s="82"/>
+      <c r="L49" s="85"/>
+      <c r="M49" s="85"/>
+      <c r="N49" s="85"/>
+      <c r="O49" s="85"/>
+      <c r="P49" s="85"/>
+      <c r="Q49" s="85"/>
+      <c r="R49" s="85"/>
+      <c r="S49" s="85"/>
+      <c r="T49" s="85"/>
+      <c r="U49" s="85"/>
+      <c r="V49" s="85"/>
+      <c r="W49" s="85"/>
+      <c r="X49" s="85"/>
+      <c r="Y49" s="85"/>
+      <c r="Z49" s="85"/>
+      <c r="AA49" s="85"/>
+      <c r="AB49" s="85"/>
+      <c r="AC49" s="85"/>
+      <c r="AD49" s="85"/>
+      <c r="AE49" s="85"/>
+      <c r="AF49" s="85"/>
       <c r="AG49" s="3" t="s">
         <v>12</v>
       </c>
@@ -4744,42 +4765,42 @@
       <c r="B52" s="17">
         <v>4</v>
       </c>
-      <c r="C52" s="88" t="s">
+      <c r="C52" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="D52" s="88"/>
-      <c r="E52" s="88"/>
-      <c r="F52" s="88"/>
-      <c r="G52" s="88"/>
-      <c r="H52" s="88"/>
-      <c r="I52" s="88"/>
-      <c r="J52" s="88"/>
-      <c r="K52" s="88"/>
-      <c r="L52" s="88"/>
-      <c r="M52" s="88"/>
-      <c r="N52" s="88"/>
-      <c r="O52" s="88"/>
-      <c r="P52" s="88"/>
-      <c r="Q52" s="88"/>
-      <c r="R52" s="88"/>
-      <c r="S52" s="88" t="s">
+      <c r="D52" s="91"/>
+      <c r="E52" s="91"/>
+      <c r="F52" s="91"/>
+      <c r="G52" s="91"/>
+      <c r="H52" s="91"/>
+      <c r="I52" s="91"/>
+      <c r="J52" s="91"/>
+      <c r="K52" s="91"/>
+      <c r="L52" s="91"/>
+      <c r="M52" s="91"/>
+      <c r="N52" s="91"/>
+      <c r="O52" s="91"/>
+      <c r="P52" s="91"/>
+      <c r="Q52" s="91"/>
+      <c r="R52" s="91"/>
+      <c r="S52" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="T52" s="88"/>
-      <c r="U52" s="88"/>
-      <c r="V52" s="88"/>
-      <c r="W52" s="88"/>
-      <c r="X52" s="88"/>
-      <c r="Y52" s="88"/>
-      <c r="Z52" s="88"/>
-      <c r="AA52" s="88"/>
-      <c r="AB52" s="88"/>
-      <c r="AC52" s="88"/>
-      <c r="AD52" s="88"/>
-      <c r="AE52" s="88"/>
-      <c r="AF52" s="88"/>
-      <c r="AG52" s="88"/>
-      <c r="AH52" s="88"/>
+      <c r="T52" s="91"/>
+      <c r="U52" s="91"/>
+      <c r="V52" s="91"/>
+      <c r="W52" s="91"/>
+      <c r="X52" s="91"/>
+      <c r="Y52" s="91"/>
+      <c r="Z52" s="91"/>
+      <c r="AA52" s="91"/>
+      <c r="AB52" s="91"/>
+      <c r="AC52" s="91"/>
+      <c r="AD52" s="91"/>
+      <c r="AE52" s="91"/>
+      <c r="AF52" s="91"/>
+      <c r="AG52" s="91"/>
+      <c r="AH52" s="91"/>
     </row>
     <row r="54" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
@@ -4788,288 +4809,288 @@
       <c r="B54" s="17">
         <v>5</v>
       </c>
-      <c r="C54" s="88" t="s">
+      <c r="C54" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="D54" s="88"/>
-      <c r="E54" s="88"/>
-      <c r="F54" s="88"/>
-      <c r="G54" s="88"/>
-      <c r="H54" s="88"/>
-      <c r="I54" s="88"/>
-      <c r="J54" s="88"/>
-      <c r="K54" s="88"/>
-      <c r="L54" s="88"/>
-      <c r="M54" s="88"/>
-      <c r="N54" s="88"/>
-      <c r="O54" s="88"/>
-      <c r="P54" s="88"/>
-      <c r="Q54" s="88"/>
-      <c r="R54" s="88"/>
-      <c r="S54" s="88" t="s">
+      <c r="D54" s="91"/>
+      <c r="E54" s="91"/>
+      <c r="F54" s="91"/>
+      <c r="G54" s="91"/>
+      <c r="H54" s="91"/>
+      <c r="I54" s="91"/>
+      <c r="J54" s="91"/>
+      <c r="K54" s="91"/>
+      <c r="L54" s="91"/>
+      <c r="M54" s="91"/>
+      <c r="N54" s="91"/>
+      <c r="O54" s="91"/>
+      <c r="P54" s="91"/>
+      <c r="Q54" s="91"/>
+      <c r="R54" s="91"/>
+      <c r="S54" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="T54" s="88"/>
-      <c r="U54" s="88"/>
-      <c r="V54" s="88"/>
-      <c r="W54" s="88"/>
-      <c r="X54" s="88"/>
-      <c r="Y54" s="88"/>
-      <c r="Z54" s="88"/>
-      <c r="AA54" s="88"/>
-      <c r="AB54" s="88"/>
-      <c r="AC54" s="88"/>
-      <c r="AD54" s="88"/>
-      <c r="AE54" s="88"/>
-      <c r="AF54" s="88"/>
-      <c r="AG54" s="88"/>
-      <c r="AH54" s="88"/>
+      <c r="T54" s="91"/>
+      <c r="U54" s="91"/>
+      <c r="V54" s="91"/>
+      <c r="W54" s="91"/>
+      <c r="X54" s="91"/>
+      <c r="Y54" s="91"/>
+      <c r="Z54" s="91"/>
+      <c r="AA54" s="91"/>
+      <c r="AB54" s="91"/>
+      <c r="AC54" s="91"/>
+      <c r="AD54" s="91"/>
+      <c r="AE54" s="91"/>
+      <c r="AF54" s="91"/>
+      <c r="AG54" s="91"/>
+      <c r="AH54" s="91"/>
     </row>
     <row r="56" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C56" s="88" t="s">
+      <c r="C56" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="D56" s="88"/>
-      <c r="E56" s="88"/>
-      <c r="F56" s="88"/>
-      <c r="G56" s="88"/>
-      <c r="H56" s="88"/>
-      <c r="I56" s="88"/>
-      <c r="J56" s="88"/>
-      <c r="K56" s="88"/>
-      <c r="L56" s="88"/>
-      <c r="M56" s="88"/>
-      <c r="N56" s="88"/>
-      <c r="O56" s="88" t="s">
+      <c r="D56" s="91"/>
+      <c r="E56" s="91"/>
+      <c r="F56" s="91"/>
+      <c r="G56" s="91"/>
+      <c r="H56" s="91"/>
+      <c r="I56" s="91"/>
+      <c r="J56" s="91"/>
+      <c r="K56" s="91"/>
+      <c r="L56" s="91"/>
+      <c r="M56" s="91"/>
+      <c r="N56" s="91"/>
+      <c r="O56" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="P56" s="88"/>
-      <c r="Q56" s="88"/>
-      <c r="R56" s="88"/>
-      <c r="S56" s="88"/>
-      <c r="T56" s="88"/>
-      <c r="U56" s="88"/>
-      <c r="V56" s="88"/>
-      <c r="W56" s="88"/>
-      <c r="X56" s="88"/>
-      <c r="Y56" s="88"/>
-      <c r="Z56" s="88"/>
-      <c r="AA56" s="88"/>
-      <c r="AB56" s="88"/>
-      <c r="AC56" s="88"/>
-      <c r="AD56" s="88"/>
-      <c r="AE56" s="88"/>
-      <c r="AF56" s="88"/>
-      <c r="AG56" s="88"/>
-      <c r="AH56" s="88"/>
+      <c r="P56" s="91"/>
+      <c r="Q56" s="91"/>
+      <c r="R56" s="91"/>
+      <c r="S56" s="91"/>
+      <c r="T56" s="91"/>
+      <c r="U56" s="91"/>
+      <c r="V56" s="91"/>
+      <c r="W56" s="91"/>
+      <c r="X56" s="91"/>
+      <c r="Y56" s="91"/>
+      <c r="Z56" s="91"/>
+      <c r="AA56" s="91"/>
+      <c r="AB56" s="91"/>
+      <c r="AC56" s="91"/>
+      <c r="AD56" s="91"/>
+      <c r="AE56" s="91"/>
+      <c r="AF56" s="91"/>
+      <c r="AG56" s="91"/>
+      <c r="AH56" s="91"/>
     </row>
     <row r="58" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C58" s="88" t="s">
+      <c r="C58" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="D58" s="88"/>
-      <c r="E58" s="88"/>
-      <c r="F58" s="88"/>
-      <c r="G58" s="88"/>
-      <c r="H58" s="88"/>
-      <c r="I58" s="88"/>
-      <c r="J58" s="88"/>
-      <c r="K58" s="88"/>
-      <c r="L58" s="88"/>
-      <c r="M58" s="88"/>
-      <c r="N58" s="88"/>
-      <c r="O58" s="88" t="s">
+      <c r="D58" s="91"/>
+      <c r="E58" s="91"/>
+      <c r="F58" s="91"/>
+      <c r="G58" s="91"/>
+      <c r="H58" s="91"/>
+      <c r="I58" s="91"/>
+      <c r="J58" s="91"/>
+      <c r="K58" s="91"/>
+      <c r="L58" s="91"/>
+      <c r="M58" s="91"/>
+      <c r="N58" s="91"/>
+      <c r="O58" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="P58" s="88"/>
-      <c r="Q58" s="88"/>
-      <c r="R58" s="88"/>
-      <c r="S58" s="88"/>
-      <c r="T58" s="88"/>
-      <c r="U58" s="88"/>
-      <c r="V58" s="88"/>
-      <c r="W58" s="88"/>
-      <c r="X58" s="88"/>
-      <c r="Y58" s="88"/>
-      <c r="Z58" s="88"/>
-      <c r="AA58" s="88"/>
-      <c r="AB58" s="88"/>
-      <c r="AC58" s="88"/>
-      <c r="AD58" s="88"/>
-      <c r="AE58" s="88"/>
-      <c r="AF58" s="88"/>
-      <c r="AG58" s="88"/>
-      <c r="AH58" s="88"/>
+      <c r="P58" s="91"/>
+      <c r="Q58" s="91"/>
+      <c r="R58" s="91"/>
+      <c r="S58" s="91"/>
+      <c r="T58" s="91"/>
+      <c r="U58" s="91"/>
+      <c r="V58" s="91"/>
+      <c r="W58" s="91"/>
+      <c r="X58" s="91"/>
+      <c r="Y58" s="91"/>
+      <c r="Z58" s="91"/>
+      <c r="AA58" s="91"/>
+      <c r="AB58" s="91"/>
+      <c r="AC58" s="91"/>
+      <c r="AD58" s="91"/>
+      <c r="AE58" s="91"/>
+      <c r="AF58" s="91"/>
+      <c r="AG58" s="91"/>
+      <c r="AH58" s="91"/>
     </row>
     <row r="60" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C60" s="88" t="s">
+      <c r="C60" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="D60" s="88"/>
-      <c r="E60" s="88"/>
-      <c r="F60" s="88"/>
-      <c r="G60" s="88"/>
-      <c r="H60" s="88"/>
-      <c r="I60" s="88"/>
-      <c r="J60" s="88"/>
-      <c r="K60" s="88"/>
-      <c r="L60" s="88"/>
-      <c r="M60" s="88"/>
-      <c r="N60" s="88"/>
-      <c r="O60" s="88"/>
-      <c r="P60" s="88"/>
-      <c r="Q60" s="88"/>
-      <c r="R60" s="88"/>
-      <c r="S60" s="88" t="s">
+      <c r="D60" s="91"/>
+      <c r="E60" s="91"/>
+      <c r="F60" s="91"/>
+      <c r="G60" s="91"/>
+      <c r="H60" s="91"/>
+      <c r="I60" s="91"/>
+      <c r="J60" s="91"/>
+      <c r="K60" s="91"/>
+      <c r="L60" s="91"/>
+      <c r="M60" s="91"/>
+      <c r="N60" s="91"/>
+      <c r="O60" s="91"/>
+      <c r="P60" s="91"/>
+      <c r="Q60" s="91"/>
+      <c r="R60" s="91"/>
+      <c r="S60" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="T60" s="88"/>
-      <c r="U60" s="88"/>
-      <c r="V60" s="88"/>
-      <c r="W60" s="88"/>
-      <c r="X60" s="88"/>
-      <c r="Y60" s="88"/>
-      <c r="Z60" s="88"/>
-      <c r="AA60" s="88"/>
-      <c r="AB60" s="88"/>
-      <c r="AC60" s="88"/>
-      <c r="AD60" s="88"/>
-      <c r="AE60" s="88"/>
-      <c r="AF60" s="88"/>
-      <c r="AG60" s="88"/>
-      <c r="AH60" s="88"/>
+      <c r="T60" s="91"/>
+      <c r="U60" s="91"/>
+      <c r="V60" s="91"/>
+      <c r="W60" s="91"/>
+      <c r="X60" s="91"/>
+      <c r="Y60" s="91"/>
+      <c r="Z60" s="91"/>
+      <c r="AA60" s="91"/>
+      <c r="AB60" s="91"/>
+      <c r="AC60" s="91"/>
+      <c r="AD60" s="91"/>
+      <c r="AE60" s="91"/>
+      <c r="AF60" s="91"/>
+      <c r="AG60" s="91"/>
+      <c r="AH60" s="91"/>
     </row>
     <row r="62" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C62" s="88" t="s">
+      <c r="C62" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="D62" s="88"/>
-      <c r="E62" s="88"/>
-      <c r="F62" s="88"/>
-      <c r="G62" s="88"/>
-      <c r="H62" s="88"/>
-      <c r="I62" s="88"/>
-      <c r="J62" s="88"/>
-      <c r="K62" s="88"/>
-      <c r="L62" s="88"/>
-      <c r="M62" s="88"/>
-      <c r="N62" s="88"/>
-      <c r="O62" s="88"/>
-      <c r="P62" s="88"/>
-      <c r="Q62" s="88"/>
-      <c r="R62" s="88"/>
-      <c r="S62" s="88" t="s">
+      <c r="D62" s="91"/>
+      <c r="E62" s="91"/>
+      <c r="F62" s="91"/>
+      <c r="G62" s="91"/>
+      <c r="H62" s="91"/>
+      <c r="I62" s="91"/>
+      <c r="J62" s="91"/>
+      <c r="K62" s="91"/>
+      <c r="L62" s="91"/>
+      <c r="M62" s="91"/>
+      <c r="N62" s="91"/>
+      <c r="O62" s="91"/>
+      <c r="P62" s="91"/>
+      <c r="Q62" s="91"/>
+      <c r="R62" s="91"/>
+      <c r="S62" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="T62" s="88"/>
-      <c r="U62" s="88"/>
-      <c r="V62" s="88"/>
-      <c r="W62" s="88"/>
-      <c r="X62" s="88"/>
-      <c r="Y62" s="88"/>
-      <c r="Z62" s="88"/>
-      <c r="AA62" s="88"/>
-      <c r="AB62" s="88"/>
-      <c r="AC62" s="88"/>
-      <c r="AD62" s="88"/>
-      <c r="AE62" s="88"/>
-      <c r="AF62" s="88"/>
-      <c r="AG62" s="88"/>
-      <c r="AH62" s="88"/>
+      <c r="T62" s="91"/>
+      <c r="U62" s="91"/>
+      <c r="V62" s="91"/>
+      <c r="W62" s="91"/>
+      <c r="X62" s="91"/>
+      <c r="Y62" s="91"/>
+      <c r="Z62" s="91"/>
+      <c r="AA62" s="91"/>
+      <c r="AB62" s="91"/>
+      <c r="AC62" s="91"/>
+      <c r="AD62" s="91"/>
+      <c r="AE62" s="91"/>
+      <c r="AF62" s="91"/>
+      <c r="AG62" s="91"/>
+      <c r="AH62" s="91"/>
     </row>
     <row r="64" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C64" s="88" t="s">
+      <c r="C64" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="D64" s="88"/>
-      <c r="E64" s="88"/>
-      <c r="F64" s="88"/>
-      <c r="G64" s="88"/>
-      <c r="H64" s="88"/>
-      <c r="I64" s="88"/>
-      <c r="J64" s="88"/>
-      <c r="K64" s="88"/>
-      <c r="L64" s="88"/>
-      <c r="M64" s="88"/>
-      <c r="N64" s="88"/>
-      <c r="O64" s="88" t="s">
+      <c r="D64" s="91"/>
+      <c r="E64" s="91"/>
+      <c r="F64" s="91"/>
+      <c r="G64" s="91"/>
+      <c r="H64" s="91"/>
+      <c r="I64" s="91"/>
+      <c r="J64" s="91"/>
+      <c r="K64" s="91"/>
+      <c r="L64" s="91"/>
+      <c r="M64" s="91"/>
+      <c r="N64" s="91"/>
+      <c r="O64" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="P64" s="88"/>
-      <c r="Q64" s="88"/>
-      <c r="R64" s="88"/>
-      <c r="S64" s="88"/>
-      <c r="T64" s="88"/>
-      <c r="U64" s="88"/>
-      <c r="V64" s="88"/>
-      <c r="W64" s="88"/>
-      <c r="X64" s="88"/>
-      <c r="Y64" s="88"/>
-      <c r="Z64" s="88"/>
-      <c r="AA64" s="88"/>
-      <c r="AB64" s="88"/>
-      <c r="AC64" s="88"/>
-      <c r="AD64" s="88"/>
-      <c r="AE64" s="88"/>
-      <c r="AF64" s="88"/>
-      <c r="AG64" s="88"/>
-      <c r="AH64" s="88"/>
+      <c r="P64" s="91"/>
+      <c r="Q64" s="91"/>
+      <c r="R64" s="91"/>
+      <c r="S64" s="91"/>
+      <c r="T64" s="91"/>
+      <c r="U64" s="91"/>
+      <c r="V64" s="91"/>
+      <c r="W64" s="91"/>
+      <c r="X64" s="91"/>
+      <c r="Y64" s="91"/>
+      <c r="Z64" s="91"/>
+      <c r="AA64" s="91"/>
+      <c r="AB64" s="91"/>
+      <c r="AC64" s="91"/>
+      <c r="AD64" s="91"/>
+      <c r="AE64" s="91"/>
+      <c r="AF64" s="91"/>
+      <c r="AG64" s="91"/>
+      <c r="AH64" s="91"/>
     </row>
     <row r="66" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C66" s="88" t="s">
+      <c r="C66" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="D66" s="88"/>
-      <c r="E66" s="88"/>
-      <c r="F66" s="88"/>
-      <c r="G66" s="88"/>
-      <c r="H66" s="88"/>
-      <c r="I66" s="88"/>
-      <c r="J66" s="88"/>
-      <c r="K66" s="88"/>
-      <c r="L66" s="88"/>
-      <c r="M66" s="88"/>
-      <c r="N66" s="88"/>
-      <c r="O66" s="88" t="s">
+      <c r="D66" s="91"/>
+      <c r="E66" s="91"/>
+      <c r="F66" s="91"/>
+      <c r="G66" s="91"/>
+      <c r="H66" s="91"/>
+      <c r="I66" s="91"/>
+      <c r="J66" s="91"/>
+      <c r="K66" s="91"/>
+      <c r="L66" s="91"/>
+      <c r="M66" s="91"/>
+      <c r="N66" s="91"/>
+      <c r="O66" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="P66" s="88"/>
-      <c r="Q66" s="88"/>
-      <c r="R66" s="88"/>
-      <c r="S66" s="88"/>
-      <c r="T66" s="88"/>
-      <c r="U66" s="88"/>
-      <c r="V66" s="88"/>
-      <c r="W66" s="88"/>
-      <c r="X66" s="88"/>
-      <c r="Y66" s="88"/>
-      <c r="Z66" s="88"/>
-      <c r="AA66" s="88"/>
-      <c r="AB66" s="88"/>
-      <c r="AC66" s="88"/>
-      <c r="AD66" s="88"/>
-      <c r="AE66" s="88"/>
-      <c r="AF66" s="88"/>
-      <c r="AG66" s="88"/>
-      <c r="AH66" s="88"/>
+      <c r="P66" s="91"/>
+      <c r="Q66" s="91"/>
+      <c r="R66" s="91"/>
+      <c r="S66" s="91"/>
+      <c r="T66" s="91"/>
+      <c r="U66" s="91"/>
+      <c r="V66" s="91"/>
+      <c r="W66" s="91"/>
+      <c r="X66" s="91"/>
+      <c r="Y66" s="91"/>
+      <c r="Z66" s="91"/>
+      <c r="AA66" s="91"/>
+      <c r="AB66" s="91"/>
+      <c r="AC66" s="91"/>
+      <c r="AD66" s="91"/>
+      <c r="AE66" s="91"/>
+      <c r="AF66" s="91"/>
+      <c r="AG66" s="91"/>
+      <c r="AH66" s="91"/>
     </row>
     <row r="67" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="6"/>
@@ -5210,60 +5231,60 @@
       <c r="C69" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D69" s="88" t="s">
+      <c r="D69" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="E69" s="88"/>
-      <c r="F69" s="88" t="s">
+      <c r="E69" s="91"/>
+      <c r="F69" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="G69" s="88"/>
-      <c r="H69" s="88"/>
-      <c r="I69" s="88" t="s">
+      <c r="G69" s="91"/>
+      <c r="H69" s="91"/>
+      <c r="I69" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="J69" s="88"/>
-      <c r="K69" s="88" t="s">
+      <c r="J69" s="91"/>
+      <c r="K69" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="L69" s="88"/>
-      <c r="M69" s="88" t="s">
+      <c r="L69" s="91"/>
+      <c r="M69" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="N69" s="88"/>
-      <c r="O69" s="88"/>
-      <c r="P69" s="88"/>
-      <c r="Q69" s="88"/>
+      <c r="N69" s="91"/>
+      <c r="O69" s="91"/>
+      <c r="P69" s="91"/>
+      <c r="Q69" s="91"/>
       <c r="R69" s="10" t="s">
         <v>51</v>
       </c>
       <c r="S69" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="T69" s="88" t="s">
+      <c r="T69" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="U69" s="88"/>
-      <c r="V69" s="88" t="s">
+      <c r="U69" s="91"/>
+      <c r="V69" s="91" t="s">
         <v>47</v>
       </c>
-      <c r="W69" s="88"/>
-      <c r="X69" s="88"/>
-      <c r="Y69" s="88" t="s">
+      <c r="W69" s="91"/>
+      <c r="X69" s="91"/>
+      <c r="Y69" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="Z69" s="88"/>
-      <c r="AA69" s="88" t="s">
+      <c r="Z69" s="91"/>
+      <c r="AA69" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="AB69" s="88"/>
-      <c r="AC69" s="88" t="s">
+      <c r="AB69" s="91"/>
+      <c r="AC69" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="AD69" s="88"/>
-      <c r="AE69" s="88"/>
-      <c r="AF69" s="88"/>
-      <c r="AG69" s="88"/>
+      <c r="AD69" s="91"/>
+      <c r="AE69" s="91"/>
+      <c r="AF69" s="91"/>
+      <c r="AG69" s="91"/>
       <c r="AH69" s="10" t="s">
         <v>51</v>
       </c>
@@ -5320,18 +5341,18 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-      <c r="S71" s="88" t="s">
+      <c r="S71" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="T71" s="88"/>
-      <c r="U71" s="88"/>
-      <c r="V71" s="88"/>
-      <c r="W71" s="88"/>
-      <c r="X71" s="88"/>
-      <c r="Y71" s="88"/>
-      <c r="Z71" s="88"/>
-      <c r="AA71" s="88"/>
-      <c r="AB71" s="88"/>
+      <c r="T71" s="91"/>
+      <c r="U71" s="91"/>
+      <c r="V71" s="91"/>
+      <c r="W71" s="91"/>
+      <c r="X71" s="91"/>
+      <c r="Y71" s="91"/>
+      <c r="Z71" s="91"/>
+      <c r="AA71" s="91"/>
+      <c r="AB71" s="91"/>
       <c r="AC71" s="3">
         <v>0</v>
       </c>
@@ -5341,26 +5362,26 @@
       <c r="AE71" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="AF71" s="88" t="s">
+      <c r="AF71" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="AG71" s="88"/>
-      <c r="AH71" s="88"/>
+      <c r="AG71" s="91"/>
+      <c r="AH71" s="91"/>
     </row>
     <row r="73" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="92" t="s">
+      <c r="A73" s="95" t="s">
         <v>57</v>
       </c>
-      <c r="C73" s="95" t="s">
+      <c r="C73" s="98" t="s">
         <v>274</v>
       </c>
-      <c r="D73" s="95"/>
-      <c r="E73" s="95"/>
-      <c r="F73" s="95"/>
-      <c r="G73" s="95"/>
-      <c r="H73" s="95"/>
-      <c r="I73" s="95"/>
-      <c r="J73" s="95"/>
+      <c r="D73" s="98"/>
+      <c r="E73" s="98"/>
+      <c r="F73" s="98"/>
+      <c r="G73" s="98"/>
+      <c r="H73" s="98"/>
+      <c r="I73" s="98"/>
+      <c r="J73" s="98"/>
       <c r="K73" s="3" t="s">
         <v>12</v>
       </c>
@@ -5385,35 +5406,35 @@
       <c r="R73" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="S73" s="90">
-        <v>0</v>
-      </c>
-      <c r="T73" s="89" t="s">
+      <c r="S73" s="93">
+        <v>0</v>
+      </c>
+      <c r="T73" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="U73" s="88" t="s">
+      <c r="U73" s="91" t="s">
         <v>58</v>
       </c>
-      <c r="V73" s="88"/>
-      <c r="W73" s="96" t="s">
+      <c r="V73" s="91"/>
+      <c r="W73" s="99" t="s">
         <v>81</v>
       </c>
-      <c r="X73" s="88" t="s">
+      <c r="X73" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="Y73" s="88"/>
-      <c r="Z73" s="88"/>
-      <c r="AA73" s="88"/>
-      <c r="AB73" s="88"/>
-      <c r="AC73" s="88"/>
-      <c r="AD73" s="88"/>
-      <c r="AE73" s="88"/>
-      <c r="AF73" s="88"/>
-      <c r="AG73" s="88"/>
-      <c r="AH73" s="88"/>
+      <c r="Y73" s="91"/>
+      <c r="Z73" s="91"/>
+      <c r="AA73" s="91"/>
+      <c r="AB73" s="91"/>
+      <c r="AC73" s="91"/>
+      <c r="AD73" s="91"/>
+      <c r="AE73" s="91"/>
+      <c r="AF73" s="91"/>
+      <c r="AG73" s="91"/>
+      <c r="AH73" s="91"/>
     </row>
     <row r="74" spans="1:34" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="92"/>
+      <c r="A74" s="95"/>
       <c r="C74" s="3" t="s">
         <v>12</v>
       </c>
@@ -5432,34 +5453,34 @@
       <c r="H74" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I74" s="95" t="s">
+      <c r="I74" s="98" t="s">
         <v>275</v>
       </c>
-      <c r="J74" s="95"/>
-      <c r="K74" s="95"/>
-      <c r="L74" s="95"/>
-      <c r="M74" s="95"/>
-      <c r="N74" s="95"/>
-      <c r="O74" s="95"/>
-      <c r="P74" s="95"/>
-      <c r="Q74" s="95"/>
-      <c r="R74" s="95"/>
-      <c r="S74" s="90"/>
-      <c r="T74" s="89"/>
-      <c r="U74" s="88"/>
-      <c r="V74" s="88"/>
-      <c r="W74" s="97"/>
-      <c r="X74" s="88"/>
-      <c r="Y74" s="88"/>
-      <c r="Z74" s="88"/>
-      <c r="AA74" s="88"/>
-      <c r="AB74" s="88"/>
-      <c r="AC74" s="88"/>
-      <c r="AD74" s="88"/>
-      <c r="AE74" s="88"/>
-      <c r="AF74" s="88"/>
-      <c r="AG74" s="88"/>
-      <c r="AH74" s="88"/>
+      <c r="J74" s="98"/>
+      <c r="K74" s="98"/>
+      <c r="L74" s="98"/>
+      <c r="M74" s="98"/>
+      <c r="N74" s="98"/>
+      <c r="O74" s="98"/>
+      <c r="P74" s="98"/>
+      <c r="Q74" s="98"/>
+      <c r="R74" s="98"/>
+      <c r="S74" s="93"/>
+      <c r="T74" s="92"/>
+      <c r="U74" s="91"/>
+      <c r="V74" s="91"/>
+      <c r="W74" s="100"/>
+      <c r="X74" s="91"/>
+      <c r="Y74" s="91"/>
+      <c r="Z74" s="91"/>
+      <c r="AA74" s="91"/>
+      <c r="AB74" s="91"/>
+      <c r="AC74" s="91"/>
+      <c r="AD74" s="91"/>
+      <c r="AE74" s="91"/>
+      <c r="AF74" s="91"/>
+      <c r="AG74" s="91"/>
+      <c r="AH74" s="91"/>
     </row>
     <row r="76" spans="1:34" x14ac:dyDescent="0.25">
       <c r="F76" s="1">
@@ -5557,45 +5578,45 @@
       <c r="F77" s="47" t="s">
         <v>277</v>
       </c>
-      <c r="G77" s="83" t="s">
+      <c r="G77" s="86" t="s">
         <v>278</v>
       </c>
-      <c r="H77" s="82"/>
-      <c r="I77" s="82"/>
-      <c r="J77" s="82"/>
-      <c r="K77" s="84"/>
-      <c r="L77" s="83" t="s">
+      <c r="H77" s="85"/>
+      <c r="I77" s="85"/>
+      <c r="J77" s="85"/>
+      <c r="K77" s="87"/>
+      <c r="L77" s="86" t="s">
         <v>279</v>
       </c>
-      <c r="M77" s="82"/>
-      <c r="N77" s="82"/>
-      <c r="O77" s="82"/>
-      <c r="P77" s="84"/>
-      <c r="Q77" s="83" t="s">
+      <c r="M77" s="85"/>
+      <c r="N77" s="85"/>
+      <c r="O77" s="85"/>
+      <c r="P77" s="87"/>
+      <c r="Q77" s="86" t="s">
         <v>280</v>
       </c>
-      <c r="R77" s="82"/>
-      <c r="S77" s="82"/>
-      <c r="T77" s="82"/>
-      <c r="U77" s="84"/>
+      <c r="R77" s="85"/>
+      <c r="S77" s="85"/>
+      <c r="T77" s="85"/>
+      <c r="U77" s="87"/>
       <c r="V77" s="47" t="s">
         <v>281</v>
       </c>
-      <c r="W77" s="82" t="s">
+      <c r="W77" s="85" t="s">
         <v>282</v>
       </c>
-      <c r="X77" s="82"/>
-      <c r="Y77" s="82"/>
-      <c r="Z77" s="83" t="s">
+      <c r="X77" s="85"/>
+      <c r="Y77" s="85"/>
+      <c r="Z77" s="86" t="s">
         <v>283</v>
       </c>
-      <c r="AA77" s="82"/>
-      <c r="AB77" s="84"/>
-      <c r="AC77" s="82" t="s">
+      <c r="AA77" s="85"/>
+      <c r="AB77" s="87"/>
+      <c r="AC77" s="85" t="s">
         <v>284</v>
       </c>
-      <c r="AD77" s="82"/>
-      <c r="AE77" s="84"/>
+      <c r="AD77" s="85"/>
+      <c r="AE77" s="87"/>
       <c r="AF77" s="47" t="s">
         <v>285</v>
       </c>
@@ -5731,128 +5752,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="85"/>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-      <c r="S1" s="85"/>
-      <c r="T1" s="85"/>
-      <c r="U1" s="85"/>
-      <c r="V1" s="85"/>
-      <c r="W1" s="85"/>
-      <c r="X1" s="85"/>
-      <c r="Y1" s="85"/>
-      <c r="Z1" s="85"/>
-      <c r="AA1" s="85"/>
-      <c r="AB1" s="85"/>
-      <c r="AC1" s="85"/>
-      <c r="AD1" s="85"/>
-      <c r="AE1" s="85"/>
-      <c r="AF1" s="85"/>
-      <c r="AG1" s="85"/>
-      <c r="AH1" s="85"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
+      <c r="V1" s="88"/>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="88"/>
+      <c r="Z1" s="88"/>
+      <c r="AA1" s="88"/>
+      <c r="AB1" s="88"/>
+      <c r="AC1" s="88"/>
+      <c r="AD1" s="88"/>
+      <c r="AE1" s="88"/>
+      <c r="AF1" s="88"/>
+      <c r="AG1" s="88"/>
+      <c r="AH1" s="88"/>
     </row>
     <row r="2" spans="1:34" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="2">
+      <c r="C2" s="74">
         <v>31</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="72">
         <v>30</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="72">
         <v>29</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="73">
         <v>28</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="74">
         <v>27</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="72">
         <v>26</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="72">
         <v>25</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="73">
         <v>24</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="74">
         <v>23</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="72">
         <v>22</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="72">
         <v>21</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="73">
         <v>20</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="74">
         <v>19</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="72">
         <v>18</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="72">
         <v>17</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="73">
         <v>16</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="74">
         <v>15</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="72">
         <v>14</v>
       </c>
-      <c r="U2" s="2">
+      <c r="U2" s="72">
         <v>13</v>
       </c>
-      <c r="V2" s="2">
-        <v>12</v>
-      </c>
-      <c r="W2" s="2">
+      <c r="V2" s="73">
+        <v>12</v>
+      </c>
+      <c r="W2" s="74">
         <v>11</v>
       </c>
-      <c r="X2" s="2">
+      <c r="X2" s="72">
         <v>10</v>
       </c>
-      <c r="Y2" s="2">
+      <c r="Y2" s="72">
         <v>9</v>
       </c>
-      <c r="Z2" s="2">
+      <c r="Z2" s="73">
         <v>8</v>
       </c>
-      <c r="AA2" s="2">
+      <c r="AA2" s="74">
         <v>7</v>
       </c>
-      <c r="AB2" s="2">
+      <c r="AB2" s="72">
         <v>6</v>
       </c>
-      <c r="AC2" s="2">
+      <c r="AC2" s="72">
         <v>5</v>
       </c>
-      <c r="AD2" s="2">
+      <c r="AD2" s="73">
         <v>4</v>
       </c>
       <c r="AE2" s="2">
@@ -5864,7 +5885,7 @@
       <c r="AG2" s="2">
         <v>1</v>
       </c>
-      <c r="AH2" s="2">
+      <c r="AH2" s="73">
         <v>0</v>
       </c>
     </row>
@@ -5893,11 +5914,11 @@
       <c r="H3" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I3" s="89" t="s">
+      <c r="I3" s="92" t="s">
         <v>83</v>
       </c>
-      <c r="J3" s="89"/>
-      <c r="K3" s="89"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
       <c r="L3" s="12" t="s">
         <v>84</v>
       </c>
@@ -5922,25 +5943,25 @@
       <c r="S3" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="T3" s="83" t="s">
+      <c r="T3" s="86" t="s">
         <v>91</v>
       </c>
-      <c r="U3" s="82"/>
-      <c r="V3" s="82"/>
-      <c r="W3" s="82"/>
-      <c r="X3" s="82"/>
-      <c r="Y3" s="84"/>
-      <c r="Z3" s="83" t="s">
+      <c r="U3" s="85"/>
+      <c r="V3" s="85"/>
+      <c r="W3" s="85"/>
+      <c r="X3" s="85"/>
+      <c r="Y3" s="87"/>
+      <c r="Z3" s="86" t="s">
         <v>92</v>
       </c>
-      <c r="AA3" s="82"/>
-      <c r="AB3" s="82"/>
-      <c r="AC3" s="82"/>
-      <c r="AD3" s="82"/>
-      <c r="AE3" s="82"/>
-      <c r="AF3" s="82"/>
-      <c r="AG3" s="82"/>
-      <c r="AH3" s="84"/>
+      <c r="AA3" s="85"/>
+      <c r="AB3" s="85"/>
+      <c r="AC3" s="85"/>
+      <c r="AD3" s="85"/>
+      <c r="AE3" s="85"/>
+      <c r="AF3" s="85"/>
+      <c r="AG3" s="85"/>
+      <c r="AH3" s="87"/>
     </row>
     <row r="5" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
@@ -5973,34 +5994,34 @@
       <c r="J5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="83" t="s">
+      <c r="K5" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="82"/>
-      <c r="M5" s="82"/>
-      <c r="N5" s="82"/>
-      <c r="O5" s="82"/>
-      <c r="P5" s="82"/>
-      <c r="Q5" s="82"/>
-      <c r="R5" s="82"/>
-      <c r="S5" s="82"/>
-      <c r="T5" s="82"/>
-      <c r="U5" s="82"/>
-      <c r="V5" s="82"/>
-      <c r="W5" s="82"/>
-      <c r="X5" s="82"/>
-      <c r="Y5" s="82"/>
-      <c r="Z5" s="82"/>
-      <c r="AA5" s="82"/>
-      <c r="AB5" s="82"/>
-      <c r="AC5" s="82"/>
-      <c r="AD5" s="82"/>
-      <c r="AE5" s="82"/>
-      <c r="AF5" s="84"/>
-      <c r="AG5" s="86" t="s">
-        <v>12</v>
-      </c>
-      <c r="AH5" s="87"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="85"/>
+      <c r="O5" s="85"/>
+      <c r="P5" s="85"/>
+      <c r="Q5" s="85"/>
+      <c r="R5" s="85"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="85"/>
+      <c r="U5" s="85"/>
+      <c r="V5" s="85"/>
+      <c r="W5" s="85"/>
+      <c r="X5" s="85"/>
+      <c r="Y5" s="85"/>
+      <c r="Z5" s="85"/>
+      <c r="AA5" s="85"/>
+      <c r="AB5" s="85"/>
+      <c r="AC5" s="85"/>
+      <c r="AD5" s="85"/>
+      <c r="AE5" s="85"/>
+      <c r="AF5" s="87"/>
+      <c r="AG5" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH5" s="90"/>
     </row>
     <row r="6" spans="1:34" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
@@ -6069,30 +6090,30 @@
       <c r="J7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K7" s="83" t="s">
+      <c r="K7" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="82"/>
-      <c r="M7" s="82"/>
-      <c r="N7" s="82"/>
-      <c r="O7" s="82"/>
-      <c r="P7" s="82"/>
-      <c r="Q7" s="82"/>
-      <c r="R7" s="82"/>
-      <c r="S7" s="82"/>
-      <c r="T7" s="82"/>
-      <c r="U7" s="82"/>
-      <c r="V7" s="82"/>
-      <c r="W7" s="82"/>
-      <c r="X7" s="82"/>
-      <c r="Y7" s="82"/>
-      <c r="Z7" s="82"/>
-      <c r="AA7" s="82"/>
-      <c r="AB7" s="82"/>
-      <c r="AC7" s="82"/>
-      <c r="AD7" s="82"/>
-      <c r="AE7" s="82"/>
-      <c r="AF7" s="82"/>
+      <c r="L7" s="85"/>
+      <c r="M7" s="85"/>
+      <c r="N7" s="85"/>
+      <c r="O7" s="85"/>
+      <c r="P7" s="85"/>
+      <c r="Q7" s="85"/>
+      <c r="R7" s="85"/>
+      <c r="S7" s="85"/>
+      <c r="T7" s="85"/>
+      <c r="U7" s="85"/>
+      <c r="V7" s="85"/>
+      <c r="W7" s="85"/>
+      <c r="X7" s="85"/>
+      <c r="Y7" s="85"/>
+      <c r="Z7" s="85"/>
+      <c r="AA7" s="85"/>
+      <c r="AB7" s="85"/>
+      <c r="AC7" s="85"/>
+      <c r="AD7" s="85"/>
+      <c r="AE7" s="85"/>
+      <c r="AF7" s="85"/>
       <c r="AG7" s="4" t="s">
         <v>12</v>
       </c>
@@ -6167,30 +6188,30 @@
       <c r="J9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K9" s="83" t="s">
+      <c r="K9" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="L9" s="82"/>
-      <c r="M9" s="82"/>
-      <c r="N9" s="82"/>
-      <c r="O9" s="82"/>
-      <c r="P9" s="82"/>
-      <c r="Q9" s="82"/>
-      <c r="R9" s="82"/>
-      <c r="S9" s="82"/>
-      <c r="T9" s="82"/>
-      <c r="U9" s="82"/>
-      <c r="V9" s="82"/>
-      <c r="W9" s="82"/>
-      <c r="X9" s="82"/>
-      <c r="Y9" s="82"/>
-      <c r="Z9" s="82"/>
-      <c r="AA9" s="82"/>
-      <c r="AB9" s="82"/>
-      <c r="AC9" s="82"/>
-      <c r="AD9" s="82"/>
-      <c r="AE9" s="82"/>
-      <c r="AF9" s="82"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="85"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="85"/>
+      <c r="P9" s="85"/>
+      <c r="Q9" s="85"/>
+      <c r="R9" s="85"/>
+      <c r="S9" s="85"/>
+      <c r="T9" s="85"/>
+      <c r="U9" s="85"/>
+      <c r="V9" s="85"/>
+      <c r="W9" s="85"/>
+      <c r="X9" s="85"/>
+      <c r="Y9" s="85"/>
+      <c r="Z9" s="85"/>
+      <c r="AA9" s="85"/>
+      <c r="AB9" s="85"/>
+      <c r="AC9" s="85"/>
+      <c r="AD9" s="85"/>
+      <c r="AE9" s="85"/>
+      <c r="AF9" s="85"/>
       <c r="AG9" s="4" t="s">
         <v>12</v>
       </c>
@@ -6199,47 +6220,47 @@
       </c>
     </row>
     <row r="12" spans="1:34" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="85" t="s">
+      <c r="A12" s="88" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="85"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="85"/>
-      <c r="J12" s="85"/>
-      <c r="K12" s="85"/>
-      <c r="L12" s="85"/>
-      <c r="M12" s="85"/>
-      <c r="N12" s="85"/>
-      <c r="O12" s="85"/>
-      <c r="P12" s="85"/>
-      <c r="Q12" s="85"/>
-      <c r="R12" s="85"/>
-      <c r="S12" s="85"/>
-      <c r="T12" s="85"/>
-      <c r="U12" s="85"/>
-      <c r="V12" s="85"/>
-      <c r="W12" s="85"/>
-      <c r="X12" s="85"/>
-      <c r="Y12" s="85"/>
-      <c r="Z12" s="85"/>
-      <c r="AA12" s="85"/>
-      <c r="AB12" s="85"/>
-      <c r="AC12" s="85"/>
-      <c r="AD12" s="85"/>
-      <c r="AE12" s="85"/>
-      <c r="AF12" s="85"/>
-      <c r="AG12" s="85"/>
-      <c r="AH12" s="85"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="88"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="88"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="88"/>
+      <c r="H12" s="88"/>
+      <c r="I12" s="88"/>
+      <c r="J12" s="88"/>
+      <c r="K12" s="88"/>
+      <c r="L12" s="88"/>
+      <c r="M12" s="88"/>
+      <c r="N12" s="88"/>
+      <c r="O12" s="88"/>
+      <c r="P12" s="88"/>
+      <c r="Q12" s="88"/>
+      <c r="R12" s="88"/>
+      <c r="S12" s="88"/>
+      <c r="T12" s="88"/>
+      <c r="U12" s="88"/>
+      <c r="V12" s="88"/>
+      <c r="W12" s="88"/>
+      <c r="X12" s="88"/>
+      <c r="Y12" s="88"/>
+      <c r="Z12" s="88"/>
+      <c r="AA12" s="88"/>
+      <c r="AB12" s="88"/>
+      <c r="AC12" s="88"/>
+      <c r="AD12" s="88"/>
+      <c r="AE12" s="88"/>
+      <c r="AF12" s="88"/>
+      <c r="AG12" s="88"/>
+      <c r="AH12" s="88"/>
     </row>
     <row r="13" spans="1:34" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="2"/>
-      <c r="C13" s="2">
+      <c r="C13" s="74">
         <v>31</v>
       </c>
       <c r="D13" s="2">
@@ -6248,7 +6269,7 @@
       <c r="E13" s="2">
         <v>29</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="73">
         <v>28</v>
       </c>
       <c r="G13" s="2">
@@ -6260,7 +6281,7 @@
       <c r="I13" s="2">
         <v>25</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="73">
         <v>24</v>
       </c>
       <c r="K13" s="2">
@@ -6272,7 +6293,7 @@
       <c r="M13" s="2">
         <v>21</v>
       </c>
-      <c r="N13" s="2">
+      <c r="N13" s="73">
         <v>20</v>
       </c>
       <c r="O13" s="2">
@@ -6284,7 +6305,7 @@
       <c r="Q13" s="2">
         <v>17</v>
       </c>
-      <c r="R13" s="2">
+      <c r="R13" s="73">
         <v>16</v>
       </c>
       <c r="S13" s="2">
@@ -6296,7 +6317,7 @@
       <c r="U13" s="2">
         <v>13</v>
       </c>
-      <c r="V13" s="2">
+      <c r="V13" s="73">
         <v>12</v>
       </c>
       <c r="W13" s="2">
@@ -6308,7 +6329,7 @@
       <c r="Y13" s="2">
         <v>9</v>
       </c>
-      <c r="Z13" s="2">
+      <c r="Z13" s="73">
         <v>8</v>
       </c>
       <c r="AA13" s="2">
@@ -6320,7 +6341,7 @@
       <c r="AC13" s="2">
         <v>5</v>
       </c>
-      <c r="AD13" s="2">
+      <c r="AD13" s="73">
         <v>4</v>
       </c>
       <c r="AE13" s="2">
@@ -6332,7 +6353,7 @@
       <c r="AG13" s="2">
         <v>1</v>
       </c>
-      <c r="AH13" s="2">
+      <c r="AH13" s="73">
         <v>0</v>
       </c>
     </row>
@@ -6344,47 +6365,47 @@
       <c r="C14" s="4">
         <v>0</v>
       </c>
-      <c r="D14" s="88" t="s">
+      <c r="D14" s="91" t="s">
         <v>99</v>
       </c>
-      <c r="E14" s="88"/>
-      <c r="F14" s="88" t="s">
+      <c r="E14" s="91"/>
+      <c r="F14" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="G14" s="88"/>
-      <c r="H14" s="88"/>
-      <c r="I14" s="88"/>
-      <c r="J14" s="88"/>
-      <c r="K14" s="89" t="s">
+      <c r="G14" s="91"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="91"/>
+      <c r="J14" s="91"/>
+      <c r="K14" s="92" t="s">
         <v>101</v>
       </c>
-      <c r="L14" s="89"/>
-      <c r="M14" s="89"/>
-      <c r="N14" s="89"/>
-      <c r="O14" s="89"/>
-      <c r="P14" s="89"/>
-      <c r="Q14" s="89"/>
-      <c r="R14" s="89"/>
-      <c r="S14" s="88" t="s">
+      <c r="L14" s="92"/>
+      <c r="M14" s="92"/>
+      <c r="N14" s="92"/>
+      <c r="O14" s="92"/>
+      <c r="P14" s="92"/>
+      <c r="Q14" s="92"/>
+      <c r="R14" s="92"/>
+      <c r="S14" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="T14" s="88"/>
-      <c r="U14" s="88"/>
-      <c r="V14" s="88"/>
-      <c r="W14" s="88"/>
-      <c r="X14" s="88"/>
-      <c r="Y14" s="88"/>
-      <c r="Z14" s="88"/>
-      <c r="AA14" s="88" t="s">
+      <c r="T14" s="91"/>
+      <c r="U14" s="91"/>
+      <c r="V14" s="91"/>
+      <c r="W14" s="91"/>
+      <c r="X14" s="91"/>
+      <c r="Y14" s="91"/>
+      <c r="Z14" s="91"/>
+      <c r="AA14" s="91" t="s">
         <v>103</v>
       </c>
-      <c r="AB14" s="88"/>
-      <c r="AC14" s="88"/>
-      <c r="AD14" s="88"/>
-      <c r="AE14" s="88"/>
-      <c r="AF14" s="88"/>
-      <c r="AG14" s="88"/>
-      <c r="AH14" s="88"/>
+      <c r="AB14" s="91"/>
+      <c r="AC14" s="91"/>
+      <c r="AD14" s="91"/>
+      <c r="AE14" s="91"/>
+      <c r="AF14" s="91"/>
+      <c r="AG14" s="91"/>
+      <c r="AH14" s="91"/>
     </row>
     <row r="15" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
@@ -6466,18 +6487,18 @@
       <c r="M16" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="N16" s="89" t="s">
+      <c r="N16" s="92" t="s">
         <v>118</v>
       </c>
-      <c r="O16" s="89"/>
-      <c r="P16" s="89" t="s">
+      <c r="O16" s="92"/>
+      <c r="P16" s="92" t="s">
         <v>119</v>
       </c>
-      <c r="Q16" s="89"/>
-      <c r="R16" s="89" t="s">
+      <c r="Q16" s="92"/>
+      <c r="R16" s="92" t="s">
         <v>120</v>
       </c>
-      <c r="S16" s="89"/>
+      <c r="S16" s="92"/>
       <c r="T16" s="11" t="s">
         <v>121</v>
       </c>
@@ -6493,18 +6514,18 @@
       <c r="X16" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="Y16" s="89" t="s">
+      <c r="Y16" s="92" t="s">
         <v>112</v>
       </c>
-      <c r="Z16" s="89"/>
-      <c r="AA16" s="89" t="s">
+      <c r="Z16" s="92"/>
+      <c r="AA16" s="92" t="s">
         <v>113</v>
       </c>
-      <c r="AB16" s="89"/>
-      <c r="AC16" s="89" t="s">
+      <c r="AB16" s="92"/>
+      <c r="AC16" s="92" t="s">
         <v>114</v>
       </c>
-      <c r="AD16" s="89"/>
+      <c r="AD16" s="92"/>
       <c r="AE16" s="11" t="s">
         <v>110</v>
       </c>
@@ -6547,36 +6568,36 @@
       <c r="J17" s="4">
         <v>0</v>
       </c>
-      <c r="K17" s="89" t="s">
+      <c r="K17" s="92" t="s">
         <v>101</v>
       </c>
-      <c r="L17" s="89"/>
-      <c r="M17" s="89"/>
-      <c r="N17" s="89"/>
-      <c r="O17" s="89"/>
-      <c r="P17" s="89"/>
-      <c r="Q17" s="89"/>
-      <c r="R17" s="89"/>
-      <c r="S17" s="88" t="s">
+      <c r="L17" s="92"/>
+      <c r="M17" s="92"/>
+      <c r="N17" s="92"/>
+      <c r="O17" s="92"/>
+      <c r="P17" s="92"/>
+      <c r="Q17" s="92"/>
+      <c r="R17" s="92"/>
+      <c r="S17" s="91" t="s">
         <v>102</v>
       </c>
-      <c r="T17" s="88"/>
-      <c r="U17" s="88"/>
-      <c r="V17" s="88"/>
-      <c r="W17" s="88"/>
-      <c r="X17" s="88"/>
-      <c r="Y17" s="88"/>
-      <c r="Z17" s="88"/>
-      <c r="AA17" s="88" t="s">
+      <c r="T17" s="91"/>
+      <c r="U17" s="91"/>
+      <c r="V17" s="91"/>
+      <c r="W17" s="91"/>
+      <c r="X17" s="91"/>
+      <c r="Y17" s="91"/>
+      <c r="Z17" s="91"/>
+      <c r="AA17" s="91" t="s">
         <v>103</v>
       </c>
-      <c r="AB17" s="88"/>
-      <c r="AC17" s="88"/>
-      <c r="AD17" s="88"/>
-      <c r="AE17" s="88"/>
-      <c r="AF17" s="88"/>
-      <c r="AG17" s="88"/>
-      <c r="AH17" s="88"/>
+      <c r="AB17" s="91"/>
+      <c r="AC17" s="91"/>
+      <c r="AD17" s="91"/>
+      <c r="AE17" s="91"/>
+      <c r="AF17" s="91"/>
+      <c r="AG17" s="91"/>
+      <c r="AH17" s="91"/>
     </row>
     <row r="18" spans="1:34" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
@@ -6720,26 +6741,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="109" t="s">
         <v>270</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
-      <c r="O1" s="106"/>
-      <c r="P1" s="106"/>
-      <c r="Q1" s="106"/>
-      <c r="R1" s="106"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C2" s="2">
@@ -6796,21 +6817,21 @@
       <c r="C3" s="45" t="s">
         <v>268</v>
       </c>
-      <c r="D3" s="86"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99"/>
-      <c r="O3" s="99"/>
-      <c r="P3" s="99"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="87"/>
+      <c r="D3" s="89"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="102"/>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102"/>
+      <c r="O3" s="102"/>
+      <c r="P3" s="102"/>
+      <c r="Q3" s="102"/>
+      <c r="R3" s="90"/>
     </row>
     <row r="5" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
@@ -6819,31 +6840,31 @@
       <c r="C5" s="45">
         <v>0</v>
       </c>
-      <c r="D5" s="104" t="s">
+      <c r="D5" s="107" t="s">
         <v>245</v>
       </c>
-      <c r="E5" s="105"/>
+      <c r="E5" s="108"/>
       <c r="F5" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="G5" s="110" t="s">
+      <c r="G5" s="113" t="s">
         <v>248</v>
       </c>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="112" t="s">
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="114"/>
+      <c r="K5" s="115" t="s">
         <v>249</v>
       </c>
-      <c r="L5" s="113"/>
-      <c r="M5" s="113"/>
-      <c r="N5" s="114"/>
-      <c r="O5" s="115" t="s">
+      <c r="L5" s="116"/>
+      <c r="M5" s="116"/>
+      <c r="N5" s="117"/>
+      <c r="O5" s="118" t="s">
         <v>250</v>
       </c>
-      <c r="P5" s="115"/>
-      <c r="Q5" s="115"/>
-      <c r="R5" s="116"/>
+      <c r="P5" s="118"/>
+      <c r="Q5" s="118"/>
+      <c r="R5" s="119"/>
     </row>
     <row r="7" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
@@ -6852,29 +6873,29 @@
       <c r="C7" s="45">
         <v>1</v>
       </c>
-      <c r="D7" s="104" t="s">
+      <c r="D7" s="107" t="s">
         <v>240</v>
       </c>
-      <c r="E7" s="105"/>
+      <c r="E7" s="108"/>
       <c r="F7" s="70" t="s">
         <v>241</v>
       </c>
-      <c r="G7" s="117" t="s">
+      <c r="G7" s="120" t="s">
         <v>246</v>
       </c>
-      <c r="H7" s="118"/>
-      <c r="I7" s="101" t="s">
+      <c r="H7" s="121"/>
+      <c r="I7" s="104" t="s">
         <v>233</v>
       </c>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="102"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="102"/>
-      <c r="Q7" s="102"/>
-      <c r="R7" s="103"/>
+      <c r="J7" s="105"/>
+      <c r="K7" s="105"/>
+      <c r="L7" s="105"/>
+      <c r="M7" s="105"/>
+      <c r="N7" s="105"/>
+      <c r="O7" s="105"/>
+      <c r="P7" s="105"/>
+      <c r="Q7" s="105"/>
+      <c r="R7" s="106"/>
     </row>
     <row r="9" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
@@ -6986,14 +7007,14 @@
         <v>0</v>
       </c>
       <c r="L13" s="31"/>
-      <c r="M13" s="107" t="s">
+      <c r="M13" s="110" t="s">
         <v>228</v>
       </c>
-      <c r="N13" s="108"/>
-      <c r="O13" s="108"/>
-      <c r="P13" s="108"/>
-      <c r="Q13" s="108"/>
-      <c r="R13" s="109"/>
+      <c r="N13" s="111"/>
+      <c r="O13" s="111"/>
+      <c r="P13" s="111"/>
+      <c r="Q13" s="111"/>
+      <c r="R13" s="112"/>
     </row>
     <row r="15" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="32" t="s">
@@ -7029,11 +7050,11 @@
       <c r="L15" s="31"/>
       <c r="M15" s="31"/>
       <c r="N15" s="31"/>
-      <c r="P15" s="107" t="s">
+      <c r="P15" s="110" t="s">
         <v>229</v>
       </c>
-      <c r="Q15" s="108"/>
-      <c r="R15" s="109"/>
+      <c r="Q15" s="111"/>
+      <c r="R15" s="112"/>
     </row>
     <row r="17" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="32" t="s">
@@ -7107,13 +7128,13 @@
       </c>
       <c r="L19" s="31"/>
       <c r="M19" s="31"/>
-      <c r="N19" s="107" t="s">
+      <c r="N19" s="110" t="s">
         <v>237</v>
       </c>
-      <c r="O19" s="108"/>
-      <c r="P19" s="108"/>
-      <c r="Q19" s="108"/>
-      <c r="R19" s="109"/>
+      <c r="O19" s="111"/>
+      <c r="P19" s="111"/>
+      <c r="Q19" s="111"/>
+      <c r="R19" s="112"/>
     </row>
     <row r="21" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="32" t="s">
@@ -7176,18 +7197,18 @@
       <c r="H23" s="30">
         <v>1</v>
       </c>
-      <c r="I23" s="101" t="s">
+      <c r="I23" s="104" t="s">
         <v>239</v>
       </c>
-      <c r="J23" s="102"/>
-      <c r="K23" s="102"/>
-      <c r="L23" s="102"/>
-      <c r="M23" s="102"/>
-      <c r="N23" s="102"/>
-      <c r="O23" s="102"/>
-      <c r="P23" s="102"/>
-      <c r="Q23" s="102"/>
-      <c r="R23" s="103"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="105"/>
+      <c r="M23" s="105"/>
+      <c r="N23" s="105"/>
+      <c r="O23" s="105"/>
+      <c r="P23" s="105"/>
+      <c r="Q23" s="105"/>
+      <c r="R23" s="106"/>
     </row>
     <row r="25" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="32" t="s">
@@ -7211,18 +7232,18 @@
       <c r="H25" s="30">
         <v>0</v>
       </c>
-      <c r="I25" s="101" t="s">
+      <c r="I25" s="104" t="s">
         <v>239</v>
       </c>
-      <c r="J25" s="102"/>
-      <c r="K25" s="102"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="102"/>
-      <c r="N25" s="102"/>
-      <c r="O25" s="102"/>
-      <c r="P25" s="102"/>
-      <c r="Q25" s="102"/>
-      <c r="R25" s="103"/>
+      <c r="J25" s="105"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="105"/>
+      <c r="M25" s="105"/>
+      <c r="N25" s="105"/>
+      <c r="O25" s="105"/>
+      <c r="P25" s="105"/>
+      <c r="Q25" s="105"/>
+      <c r="R25" s="106"/>
     </row>
     <row r="27" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="32" t="s">
@@ -7246,18 +7267,18 @@
       <c r="H27" s="30">
         <v>1</v>
       </c>
-      <c r="I27" s="101" t="s">
+      <c r="I27" s="104" t="s">
         <v>239</v>
       </c>
-      <c r="J27" s="102"/>
-      <c r="K27" s="102"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="102"/>
-      <c r="N27" s="102"/>
-      <c r="O27" s="102"/>
-      <c r="P27" s="102"/>
-      <c r="Q27" s="102"/>
-      <c r="R27" s="103"/>
+      <c r="J27" s="105"/>
+      <c r="K27" s="105"/>
+      <c r="L27" s="105"/>
+      <c r="M27" s="105"/>
+      <c r="N27" s="105"/>
+      <c r="O27" s="105"/>
+      <c r="P27" s="105"/>
+      <c r="Q27" s="105"/>
+      <c r="R27" s="106"/>
     </row>
     <row r="29" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="32" t="s">
@@ -7289,12 +7310,12 @@
       <c r="N29" s="63" t="s">
         <v>259</v>
       </c>
-      <c r="O29" s="100" t="s">
+      <c r="O29" s="103" t="s">
         <v>261</v>
       </c>
-      <c r="P29" s="100"/>
-      <c r="Q29" s="100"/>
-      <c r="R29" s="100"/>
+      <c r="P29" s="103"/>
+      <c r="Q29" s="103"/>
+      <c r="R29" s="103"/>
     </row>
     <row r="31" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="32" t="s">
@@ -7318,40 +7339,40 @@
       <c r="H31" s="44" t="s">
         <v>253</v>
       </c>
-      <c r="I31" s="101" t="s">
+      <c r="I31" s="104" t="s">
         <v>233</v>
       </c>
-      <c r="J31" s="102"/>
-      <c r="K31" s="102"/>
-      <c r="L31" s="102"/>
-      <c r="M31" s="102"/>
-      <c r="N31" s="102"/>
-      <c r="O31" s="102"/>
-      <c r="P31" s="102"/>
-      <c r="Q31" s="102"/>
-      <c r="R31" s="103"/>
+      <c r="J31" s="105"/>
+      <c r="K31" s="105"/>
+      <c r="L31" s="105"/>
+      <c r="M31" s="105"/>
+      <c r="N31" s="105"/>
+      <c r="O31" s="105"/>
+      <c r="P31" s="105"/>
+      <c r="Q31" s="105"/>
+      <c r="R31" s="106"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="106" t="s">
+      <c r="A33" s="109" t="s">
         <v>269</v>
       </c>
-      <c r="B33" s="106"/>
-      <c r="C33" s="106"/>
-      <c r="D33" s="106"/>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
-      <c r="I33" s="106"/>
-      <c r="J33" s="106"/>
-      <c r="K33" s="106"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="106"/>
-      <c r="N33" s="106"/>
-      <c r="O33" s="106"/>
-      <c r="P33" s="106"/>
-      <c r="Q33" s="106"/>
-      <c r="R33" s="106"/>
+      <c r="B33" s="109"/>
+      <c r="C33" s="109"/>
+      <c r="D33" s="109"/>
+      <c r="E33" s="109"/>
+      <c r="F33" s="109"/>
+      <c r="G33" s="109"/>
+      <c r="H33" s="109"/>
+      <c r="I33" s="109"/>
+      <c r="J33" s="109"/>
+      <c r="K33" s="109"/>
+      <c r="L33" s="109"/>
+      <c r="M33" s="109"/>
+      <c r="N33" s="109"/>
+      <c r="O33" s="109"/>
+      <c r="P33" s="109"/>
+      <c r="Q33" s="109"/>
+      <c r="R33" s="109"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C34" s="2">
@@ -7407,24 +7428,24 @@
       <c r="A35" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="C35" s="98" t="s">
+      <c r="C35" s="101" t="s">
         <v>265</v>
       </c>
-      <c r="D35" s="98"/>
-      <c r="E35" s="86"/>
-      <c r="F35" s="99"/>
-      <c r="G35" s="99"/>
-      <c r="H35" s="99"/>
-      <c r="I35" s="99"/>
-      <c r="J35" s="99"/>
-      <c r="K35" s="99"/>
-      <c r="L35" s="99"/>
-      <c r="M35" s="99"/>
-      <c r="N35" s="99"/>
-      <c r="O35" s="99"/>
-      <c r="P35" s="99"/>
-      <c r="Q35" s="99"/>
-      <c r="R35" s="87"/>
+      <c r="D35" s="101"/>
+      <c r="E35" s="89"/>
+      <c r="F35" s="102"/>
+      <c r="G35" s="102"/>
+      <c r="H35" s="102"/>
+      <c r="I35" s="102"/>
+      <c r="J35" s="102"/>
+      <c r="K35" s="102"/>
+      <c r="L35" s="102"/>
+      <c r="M35" s="102"/>
+      <c r="N35" s="102"/>
+      <c r="O35" s="102"/>
+      <c r="P35" s="102"/>
+      <c r="Q35" s="102"/>
+      <c r="R35" s="90"/>
     </row>
     <row r="37" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="32" t="s">
@@ -7436,30 +7457,30 @@
       <c r="D37" s="40" t="s">
         <v>263</v>
       </c>
-      <c r="E37" s="100" t="s">
+      <c r="E37" s="103" t="s">
         <v>264</v>
       </c>
-      <c r="F37" s="100"/>
-      <c r="G37" s="100"/>
-      <c r="H37" s="100"/>
+      <c r="F37" s="103"/>
+      <c r="G37" s="103"/>
+      <c r="H37" s="103"/>
       <c r="I37" s="40" t="s">
         <v>258</v>
       </c>
-      <c r="J37" s="100" t="s">
+      <c r="J37" s="103" t="s">
         <v>260</v>
       </c>
-      <c r="K37" s="100"/>
-      <c r="L37" s="100"/>
-      <c r="M37" s="100"/>
+      <c r="K37" s="103"/>
+      <c r="L37" s="103"/>
+      <c r="M37" s="103"/>
       <c r="N37" s="41" t="s">
         <v>259</v>
       </c>
-      <c r="O37" s="100" t="s">
+      <c r="O37" s="103" t="s">
         <v>261</v>
       </c>
-      <c r="P37" s="100"/>
-      <c r="Q37" s="100"/>
-      <c r="R37" s="100"/>
+      <c r="P37" s="103"/>
+      <c r="Q37" s="103"/>
+      <c r="R37" s="103"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="I38" s="2"/>
@@ -7467,26 +7488,26 @@
     </row>
     <row r="39" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="32"/>
-      <c r="C39" s="98" t="s">
+      <c r="C39" s="101" t="s">
         <v>265</v>
       </c>
-      <c r="D39" s="98"/>
+      <c r="D39" s="101"/>
       <c r="E39" s="39" t="s">
         <v>266</v>
       </c>
-      <c r="F39" s="86"/>
-      <c r="G39" s="99"/>
-      <c r="H39" s="99"/>
-      <c r="I39" s="99"/>
-      <c r="J39" s="99"/>
-      <c r="K39" s="99"/>
-      <c r="L39" s="99"/>
-      <c r="M39" s="99"/>
-      <c r="N39" s="99"/>
-      <c r="O39" s="99"/>
-      <c r="P39" s="99"/>
-      <c r="Q39" s="99"/>
-      <c r="R39" s="87"/>
+      <c r="F39" s="89"/>
+      <c r="G39" s="102"/>
+      <c r="H39" s="102"/>
+      <c r="I39" s="102"/>
+      <c r="J39" s="102"/>
+      <c r="K39" s="102"/>
+      <c r="L39" s="102"/>
+      <c r="M39" s="102"/>
+      <c r="N39" s="102"/>
+      <c r="O39" s="102"/>
+      <c r="P39" s="102"/>
+      <c r="Q39" s="102"/>
+      <c r="R39" s="90"/>
     </row>
     <row r="41" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="32" t="s">
@@ -7510,18 +7531,18 @@
       <c r="H41" s="42" t="s">
         <v>253</v>
       </c>
-      <c r="I41" s="101" t="s">
+      <c r="I41" s="104" t="s">
         <v>233</v>
       </c>
-      <c r="J41" s="102"/>
-      <c r="K41" s="102"/>
-      <c r="L41" s="102"/>
-      <c r="M41" s="102"/>
-      <c r="N41" s="102"/>
-      <c r="O41" s="102"/>
-      <c r="P41" s="102"/>
-      <c r="Q41" s="102"/>
-      <c r="R41" s="103"/>
+      <c r="J41" s="105"/>
+      <c r="K41" s="105"/>
+      <c r="L41" s="105"/>
+      <c r="M41" s="105"/>
+      <c r="N41" s="105"/>
+      <c r="O41" s="105"/>
+      <c r="P41" s="105"/>
+      <c r="Q41" s="105"/>
+      <c r="R41" s="106"/>
     </row>
     <row r="43" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="32" t="s">
@@ -7548,21 +7569,21 @@
       <c r="I43" s="40" t="s">
         <v>258</v>
       </c>
-      <c r="J43" s="100" t="s">
+      <c r="J43" s="103" t="s">
         <v>260</v>
       </c>
-      <c r="K43" s="100"/>
-      <c r="L43" s="100"/>
-      <c r="M43" s="100"/>
+      <c r="K43" s="103"/>
+      <c r="L43" s="103"/>
+      <c r="M43" s="103"/>
       <c r="N43" s="41" t="s">
         <v>259</v>
       </c>
-      <c r="O43" s="100" t="s">
+      <c r="O43" s="103" t="s">
         <v>261</v>
       </c>
-      <c r="P43" s="100"/>
-      <c r="Q43" s="100"/>
-      <c r="R43" s="100"/>
+      <c r="P43" s="103"/>
+      <c r="Q43" s="103"/>
+      <c r="R43" s="103"/>
     </row>
     <row r="45" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="32" t="s">
@@ -7577,21 +7598,21 @@
       <c r="E45" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="F45" s="107" t="s">
+      <c r="F45" s="110" t="s">
         <v>242</v>
       </c>
-      <c r="G45" s="108"/>
-      <c r="H45" s="108"/>
-      <c r="I45" s="108"/>
-      <c r="J45" s="108"/>
-      <c r="K45" s="108"/>
-      <c r="L45" s="108"/>
-      <c r="M45" s="108"/>
-      <c r="N45" s="108"/>
-      <c r="O45" s="108"/>
-      <c r="P45" s="108"/>
-      <c r="Q45" s="108"/>
-      <c r="R45" s="109"/>
+      <c r="G45" s="111"/>
+      <c r="H45" s="111"/>
+      <c r="I45" s="111"/>
+      <c r="J45" s="111"/>
+      <c r="K45" s="111"/>
+      <c r="L45" s="111"/>
+      <c r="M45" s="111"/>
+      <c r="N45" s="111"/>
+      <c r="O45" s="111"/>
+      <c r="P45" s="111"/>
+      <c r="Q45" s="111"/>
+      <c r="R45" s="112"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -7636,7 +7657,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="25.5703125" customWidth="1"/>
+    <col min="7" max="7" width="32.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -7692,12 +7713,12 @@
       <c r="O3" s="48">
         <v>1</v>
       </c>
-      <c r="P3" s="119" t="s">
+      <c r="P3" s="122" t="s">
         <v>297</v>
       </c>
-      <c r="Q3" s="119"/>
-      <c r="R3" s="119"/>
-      <c r="S3" s="119"/>
+      <c r="Q3" s="122"/>
+      <c r="R3" s="122"/>
+      <c r="S3" s="122"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B4" s="50">
@@ -7768,7 +7789,9 @@
       <c r="F8" s="50">
         <v>5</v>
       </c>
-      <c r="G8" s="58"/>
+      <c r="G8" s="58" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B9" s="50">
